--- a/historial/recibos.xlsx
+++ b/historial/recibos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recibos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Recibos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:G349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +447,11 @@
           <t>Estado</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>DatosJSON</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -464,15 +469,12 @@
           <t>12/05/2025</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>5000000</v>
-      </c>
       <c r="E2" t="n">
-        <v>4188839</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Anulado</t>
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000001", "fecha": "12/05/2025", "cliente": "Cofaral", "domicilio": "Catamarca 1053", "localidad": "SMT", "cuit": "30-56-8596-3", "iva": "", "concepto": "", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 0.0}</t>
         </is>
       </c>
     </row>
@@ -484,23 +486,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>COFARAL</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>12/05/1999</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>6000000</v>
+          <t>ANULADO</t>
+        </is>
       </c>
       <c r="E3" t="n">
-        <v>5302122</v>
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000002", "fecha": "", "cliente": "ANULADO", "domicilio": "Localidad:", "localidad": "CUIT:", "cuit": "", "iva": "", "concepto": "", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 0.0}</t>
         </is>
       </c>
     </row>
@@ -510,9 +509,22 @@
           <t>0001-00000004</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>12/05/1999</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000004", "fecha": "12/05/1999", "cliente": "", "domicilio": "", "localidad": "", "cuit": "", "iva": "", "concepto": "", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 0.0}</t>
         </is>
       </c>
     </row>
@@ -522,9 +534,27 @@
           <t>0001-00000035</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Cofaral</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>20/08/2025</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6908718.08</v>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000035", "fecha": "20/08/2025", "cliente": "Cofaral", "domicilio": "Catamarca 1053", "localidad": "SMT", "cuit": "30-85896356-9", "iva": "Exento", "concepto": "Pago Factura 19345", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 6908718.08}</t>
         </is>
       </c>
     </row>
@@ -534,9 +564,27 @@
           <t>0001-00000040</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Cofaral</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>20/08/2025</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6745232</v>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000040", "fecha": "20/08/2025", "cliente": "Cofaral", "domicilio": "Catamarca 1053", "localidad": "SMT", "cuit": "30-85896356-9", "iva": "Exento", "concepto": "Pago Factura 19875", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 6745232.0}</t>
         </is>
       </c>
     </row>
@@ -546,9 +594,27 @@
           <t>0001-00000041</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DR. Felipe S. Palazzo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>20/08/2025</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>136586.25</v>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000041", "fecha": "20/08/2025", "cliente": "DR. Felipe S. Palazzo", "domicilio": "Sarmiento 157", "localidad": "San Miguel de Tucuman", "cuit": "20-22073820-6", "iva": "Exento", "concepto": "Pago Factura 19356", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 136586.25}</t>
         </is>
       </c>
     </row>
@@ -558,9 +624,27 @@
           <t>0001-00000042</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DR. Felipe S. Palazzo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>20/08/2025</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>136586.25</v>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000042", "fecha": "20/08/2025", "cliente": "DR. Felipe S. Palazzo", "domicilio": "Sarmiento 157", "localidad": "San Miguel de Tucuman", "cuit": "20-22073820-6", "iva": "Exento", "concepto": "Pago Factura 19356", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 136586.25}</t>
         </is>
       </c>
     </row>
@@ -570,9 +654,27 @@
           <t>0001-00000057</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ministerio de salud</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>22/08/2025</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2051566.87</v>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000057", "fecha": "22/08/2025", "cliente": "Ministerio de salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago Liquidacion 441-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 2051566.87}</t>
         </is>
       </c>
     </row>
@@ -582,9 +684,27 @@
           <t>0001-00000060</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ministerio de salud</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>22/08/2025</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>15924908.31</v>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000060", "fecha": "22/08/2025", "cliente": "Ministerio de salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago liquidacion 525-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 15924908.31}</t>
         </is>
       </c>
     </row>
@@ -594,9 +714,27 @@
           <t>0001-00000045</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ministerio de salud</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>22/08/2025</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1287668.32</v>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000045", "fecha": "22/08/2025", "cliente": "Ministerio de salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago Liquidacion 3109/2024", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1287668.32}</t>
         </is>
       </c>
     </row>
@@ -606,9 +744,27 @@
           <t>0001-00000046</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ministerio de salud</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>22/08/2025</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>14142761.41</v>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000046", "fecha": "22/08/2025", "cliente": "Ministerio de salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago Liquidacion 577/2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 14142761.41}</t>
         </is>
       </c>
     </row>
@@ -618,9 +774,27 @@
           <t>0001-00000047</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ministerio de salud</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>22/08/2025</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2607298.11</v>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000047", "fecha": "22/08/2025", "cliente": "Ministerio de salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago Liquidacion 3151/2024", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 2607298.11}</t>
         </is>
       </c>
     </row>
@@ -630,9 +804,27 @@
           <t>0001-00000048</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ministerio de salud</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>22/08/2025</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>211293.33</v>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000048", "fecha": "22/08/2025", "cliente": "Ministerio de salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago Liquidaciones 3333-2024/ 610-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 211293.33}</t>
         </is>
       </c>
     </row>
@@ -642,9 +834,27 @@
           <t>0001-00000049</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ministerio de salud</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>22/08/2025</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1540235.36</v>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000049", "fecha": "22/08/2025", "cliente": "Ministerio de salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago Liquidacion 630-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1540235.36}</t>
         </is>
       </c>
     </row>
@@ -654,9 +864,27 @@
           <t>0001-00000050</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ministerio de salud</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>22/08/2025</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>11851294.24</v>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000050", "fecha": "22/08/2025", "cliente": "Ministerio de salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago Liquidacion 478-2025 / 3198-2024", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 11851294.24}</t>
         </is>
       </c>
     </row>
@@ -666,9 +894,27 @@
           <t>0001-00000051</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ministerio de salud</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>22/08/2025</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5287313.46</v>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000051", "fecha": "22/08/2025", "cliente": "Ministerio de salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago Liquidacion 575-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 5287313.46}</t>
         </is>
       </c>
     </row>
@@ -678,9 +924,27 @@
           <t>0001-00000052</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ministerio de salud</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>22/08/2025</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3457419.86</v>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000052", "fecha": "22/08/2025", "cliente": "Ministerio de salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago Liquidacion 599-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 3457419.86}</t>
         </is>
       </c>
     </row>
@@ -690,9 +954,27 @@
           <t>0001-00000053</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ministerio de salud</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>22/08/2025</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>3749248.41</v>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000053", "fecha": "22/08/2025", "cliente": "Ministerio de salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago Liquidacion 570-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 3749248.41}</t>
         </is>
       </c>
     </row>
@@ -702,9 +984,27 @@
           <t>0001-00000054</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ministerio de salud</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>22/08/2025</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1914063.23</v>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000054", "fecha": "22/08/2025", "cliente": "Ministerio de salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago Liquidacion 453-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1914063.23}</t>
         </is>
       </c>
     </row>
@@ -714,9 +1014,27 @@
           <t>0001-00000055</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ministerio de salud</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>22/08/2025</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>15924908.31</v>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000055", "fecha": "22/08/2025", "cliente": "Ministerio de salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago Liquidacion 525-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 15924908.31}</t>
         </is>
       </c>
     </row>
@@ -726,9 +1044,27 @@
           <t>0001-00000056</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ministerio de salud</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>22/08/2025</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2051566.87</v>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000056", "fecha": "22/08/2025", "cliente": "Ministerio de salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago Liquidacion 441-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 2051566.87}</t>
         </is>
       </c>
     </row>
@@ -738,9 +1074,27 @@
           <t>0001-00000058</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ministerio de salud</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>22/08/2025</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5346887.97</v>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000058", "fecha": "22/08/2025", "cliente": "Ministerio de salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago Liquidacion 3214-2025 / 497-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 5346887.97}</t>
         </is>
       </c>
     </row>
@@ -750,9 +1104,27 @@
           <t>0001-00000059</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ministerio de salud</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>22/08/2025</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>3971830.54</v>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000059", "fecha": "22/08/2025", "cliente": "Ministerio de salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago Liquidacion 414-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 3971830.54}</t>
         </is>
       </c>
     </row>
@@ -762,9 +1134,27 @@
           <t>0001-00000061</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ministerio de salud</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>22/08/2025</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>15924908.31</v>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000061", "fecha": "22/08/2025", "cliente": "Ministerio de salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago liquidacion 525-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 15924908.31}</t>
         </is>
       </c>
     </row>
@@ -774,9 +1164,27 @@
           <t>0001-00000062</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>22/08/2025</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5346887.97</v>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000062", "fecha": "22/08/2025", "cliente": "Ministerio de Salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago liquidacion 497-2025 / 3214-2024", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 5346887.97}</t>
         </is>
       </c>
     </row>
@@ -786,9 +1194,27 @@
           <t>0001-00000063</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>22/08/2025</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>3971830.54</v>
+      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000063", "fecha": "22/08/2025", "cliente": "Ministerio de Salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago liquidacion 414-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 3971830.54}</t>
         </is>
       </c>
     </row>
@@ -798,9 +1224,27 @@
           <t>0001-00000068</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Aliar S.A.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>25/08/2025</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5866665.4</v>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000068", "fecha": "25/08/2025", "cliente": "Aliar S.A.", "domicilio": "San Miguel de Tucuman", "localidad": "San Miguel de Tucuman", "cuit": "30-70792118-4", "iva": "Responsable Inscripto", "concepto": "Pago Facturas 19227 / 19264", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 5866665.4}</t>
         </is>
       </c>
     </row>
@@ -810,9 +1254,27 @@
           <t>0001-00000102</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>O.S. Del Personal Mosaista</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>27/08/2025</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2300000</v>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000102", "fecha": "27/08/2025", "cliente": "O.S. Del Personal Mosaista", "domicilio": "Quirno 89", "localidad": "CABA", "cuit": "30-60658818-2", "iva": "Inscripto", "concepto": "Pago Facturas 23676 ($4.947) / 23684 ($87.229) / 23690($20.532) / 23700($57477) / 23701($320.391) /\n23706($5.258) / 23709($86.684) / 23711($5.993) / 23722($57.477) / 23723($10.266) / 23724($57.477) /\n23725($161.206) / 23742($5.993) / 23749($23.310) / 23753 ($488.330) / 23816($5.592) / 23817($135.563) /\n23831($58.176) / 23837($148.678) / 23851($51.030) / 23899($5.366) / 23917 ($4.947) / 23932($498.078)", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 2300000.0}</t>
         </is>
       </c>
     </row>
@@ -822,9 +1284,27 @@
           <t>0001-00000103</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>O.S. Del Personal Mosaista</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>27/08/2025</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2300000</v>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000103", "fecha": "27/08/2025", "cliente": "O.S. Del Personal Mosaista", "domicilio": "Quirno 89", "localidad": "CABA", "cuit": "30-60658818-2", "iva": "Inscripto", "concepto": "Pago Facturas 23676 ($4.947) / 23684 ($87.229) / 23690($20.532) / 23700($57477) / 23701($320.391) /\n23706($5.258) / 23709($86.684) / 23711($5.993) / 23722($57.477) / 23723($10.266) / 23724($57.477) /\n23725($161.206) / 23742($5.993) / 23749($23.310) / 23753 ($488.330) / 23816($5.592) / 23817($135.563) /\n23831($58.176) / 23837($148.678) / 23851($51.030) / 23899($5.366) / 23917 ($4.947) / 23932($498.078)", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 2300000.0}</t>
         </is>
       </c>
     </row>
@@ -834,9 +1314,27 @@
           <t>0001-00000104</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>O.S. Del Personal Mosaista</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>27/08/2025</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>2300000</v>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000104", "fecha": "27/08/2025", "cliente": "O.S. Del Personal Mosaista", "domicilio": "Quirno 89", "localidad": "CABA", "cuit": "30-60658818-2", "iva": "Inscripto", "concepto": "Pago Facturas 23676 ($4.947) / 23684 ($87.229) / 23690($20.532) / 23700($57477) / 23701($320.391) /\n23706($5.258) / 23709($86.684) / 23711($5.993) / 23722($57.477) / 23723($10.266) / 23724($57.477) /\n23725($161.206) / 23742($5.993) / 23749($23.310) / 23753 ($488.330) / 23816($5.592) / 23817($135.563) /\n23831($58.176) / 23837($148.678) / 23851($51.030) / 23899($5.366) / 23917 ($4.947) / 23932($498.078)", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 2300000.0}</t>
         </is>
       </c>
     </row>
@@ -846,9 +1344,27 @@
           <t>0001-00000107</t>
         </is>
       </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>O.S. Del Personal Mosaista</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>27/08/2025</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>15100000</v>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000107", "fecha": "27/08/2025", "cliente": "O.S. Del Personal Mosaista", "domicilio": "Quirno 89", "localidad": "CABA", "cuit": "30-60658818-2", "iva": "Inscripto", "concepto": "Pago Facturas 21816($7.035.128)/ 22462($185942) / 22537($781.633) / 22554($344059) / 22584($4.354.400) / 22596($275.350) /\n22698($22.194) / 22711($459.251) / 22743($305.344) / 22850($5.141) / 22863($5.468) / 22987($65.405) / 22992($447.190) /\n22993($54.722) / 22995($105…", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 15100000.0}</t>
         </is>
       </c>
     </row>
@@ -858,9 +1374,27 @@
           <t>0001-00000109</t>
         </is>
       </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>O.S. Del Personal Mosaista</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>27/08/2025</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>15100000</v>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000109", "fecha": "27/08/2025", "cliente": "O.S. Del Personal Mosaista", "domicilio": "Quirno 89", "localidad": "CABA", "cuit": "30-60658818-2", "iva": "Inscripto", "concepto": "Pago Facturas 21816($7.035.128)/ 22462($185942) / 22537($781.633) / 22554($344059) / 22584($4.354.400) / 22596($275.350) /\n22698($22.194) / 22711($459.251) / 22743($305.344) / 22850($5.141) / 22863($5.468) / 22987($65.405) / 229…\nPago Facturas 21816($7.035.128)/ 22462($185942) / 22537($781.633) / 22554($344059) / 22584($4.354.400) / 22596($275.350) /\n22698($22.194) / 22711($459.251) / 22743($305.344) / 22850($5.141) / 22863($5.468) / 22987($65.405) / 22992($447.190) /…", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 15100000.0}</t>
         </is>
       </c>
     </row>
@@ -870,13 +1404,8043 @@
           <t>0001-00000110</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>O.S. Del Personal Mosaista</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>27/08/2025</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>15100000</v>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000110", "fecha": "27/08/2025", "cliente": "O.S. Del Personal Mosaista", "domicilio": "Quirno 89", "localidad": "CABA", "cuit": "30-60658818-2", "iva": "Inscripto", "concepto": "Pago Facturas 21816($7.035.128)/ 22462($185942) / 22537($781.633) / 22554($344059) / 22584($4.354.400) /\n22596($275.350) / 22698($22.194) / 22711($459.251) / 22743($305.344) / 22850($5.141) / 22863($5.468) /\n22987($65.405) / 22992($447.190) / 22993($54.722) / 22995($105.377) / 22996($105.377) / 22999($54.722) /\n23002($5.468) / 23134($54.722) / 23141($69.124) / 23309($5.859) / 23340($5.859)", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 15100000.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>0001-00000351</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Recibo de Prueba</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="n">
+        <v>560000</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000351", "fecha": "03/11/2025", "cliente": "Recibo de Prueba", "domicilio": "Lamadrid 264", "localidad": "SMT", "cuit": "30-63928547-8", "iva": "Exento", "concepto": "PAgo algo de fa", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 560000.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>0001-99999999</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Cliente Prueba</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>01/11/2025</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1234.56</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-99999999", "cliente": "Cliente Prueba", "total": 1234.56}</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>0001-00000003</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000003", "fecha": "", "cliente": "", "domicilio": "", "localidad": "", "cuit": "", "iva": "", "concepto": "", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 0.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>0001-00000005</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>11/08/2025</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000005", "fecha": "11/08/2025", "cliente": "", "domicilio": "", "localidad": "", "cuit": "", "iva": "", "concepto": "", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 0.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>0001-00000006</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>14/08/2025</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000006", "fecha": "14/08/2025", "cliente": "", "domicilio": "", "localidad": "", "cuit": "", "iva": "", "concepto": "", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 0.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>0001-00000007</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>O.S. del Personal mosaista</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>14/08/2025</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>4332083</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000007", "fecha": "14/08/2025", "cliente": "O.S. del Personal mosaista", "domicilio": "Quirno 89", "localidad": "CABA", "cuit": "30-60658818-2", "iva": "Exento", "concepto": "ndsalndwiu", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 4332083.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>0001-00000008</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>O.S. del Personal Mosaista</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>15/08/2025</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5208748</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000008", "fecha": "15/08/2025", "cliente": "O.S. del Personal Mosaista", "domicilio": "Quirno 89", "localidad": "CABA", "cuit": "30-60658818-2", "iva": "Exento", "concepto": "Pago Factura 15669", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 5208748.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>0001-00000009</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>O.S. del Personal Mosaista</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>15/08/2025</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>5208748</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000009", "fecha": "15/08/2025", "cliente": "O.S. del Personal Mosaista", "domicilio": "Quirno 89", "localidad": "CABA", "cuit": "30-60658818-2", "iva": "Exento", "concepto": "Pago Factura 15669", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 5208748.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0001-00000010</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>O.S. del Personal Mosaista</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>15/08/2025</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>409695</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000010", "fecha": "15/08/2025", "cliente": "O.S. del Personal Mosaista", "domicilio": "Quirno 89", "localidad": "CABA", "cuit": "30-60658818-2", "iva": "Exento", "concepto": "Pago factura 14588", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 409695.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>0001-00000011</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>O.S. del personal mosaista</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>18/08/2025</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000011", "fecha": "18/08/2025", "cliente": "O.S. del personal mosaista", "domicilio": "Quirno 89", "localidad": "CABA", "cuit": "30-60658818-2", "iva": "Exento", "concepto": "Pago factura 18963", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>0001-00000012</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>O.S. del personal mosaista</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>18/08/2025</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000012", "fecha": "18/08/2025", "cliente": "O.S. del personal mosaista", "domicilio": "Quirno 89", "localidad": "CABA", "cuit": "30-60658818-2", "iva": "Exento", "concepto": "Pago factura■17896", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>0001-00000013</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>O.S. del personal mosaista</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>18/08/2025</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000013", "fecha": "18/08/2025", "cliente": "O.S. del personal mosaista", "domicilio": "Quirno 89", "localidad": "CABA", "cuit": "30-60658818-2", "iva": "Exento", "concepto": "Pago factura 14898", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>0001-00000014</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>O.S. Del Personal Mosaista</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>18/08/2025</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000014", "fecha": "18/08/2025", "cliente": "O.S. Del Personal Mosaista", "domicilio": "Quirno 89", "localidad": "CABA", "cuit": "30-60658818-2", "iva": "Exento", "concepto": "Pago factura 18579", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>0001-00000015</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Cofaral</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>18/08/2025</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000015", "fecha": "18/08/2025", "cliente": "Cofaral", "domicilio": "", "localidad": "", "cuit": "", "iva": "", "concepto": "", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>0001-00000016</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Cofaral</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>18/08/2025</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1569983</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000016", "fecha": "18/08/2025", "cliente": "Cofaral", "domicilio": "", "localidad": "", "cuit": "", "iva": "", "concepto": "", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1569983.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>0001-00000017</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Cofaral</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>18/08/2025</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000017", "fecha": "18/08/2025", "cliente": "Cofaral", "domicilio": "Catamarca 1053", "localidad": "SMT", "cuit": "30-85896356-9", "iva": "Exento", "concepto": "Pago factura 18578", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>0001-00000018</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Cofaral</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>18/08/2025</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000018", "fecha": "18/08/2025", "cliente": "Cofaral", "domicilio": "Catamarca 1053", "localidad": "SMT", "cuit": "30-85896356-9", "iva": "Exento", "concepto": "Pago Factura 18546", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>0001-00000019</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>O.S. Del Personal Mosaista</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>19/08/2025</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000019", "fecha": "19/08/2025", "cliente": "O.S. Del Personal Mosaista", "domicilio": "Quirno 89", "localidad": "CABA", "cuit": "30-60658818-2", "iva": "Exento", "concepto": "Pago actura 19856", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>0001-00000020</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>O.S. Del Personal Mosaista</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>19/08/2025</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000020", "fecha": "19/08/2025", "cliente": "O.S. Del Personal Mosaista", "domicilio": "Quirno 89", "localidad": "CABA", "cuit": "30-60658818-2", "iva": "Exento", "concepto": "Pago factura 18578", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>0001-00000021</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Cofaral</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>19/08/2025</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000021", "fecha": "19/08/2025", "cliente": "Cofaral", "domicilio": "Catamarca 1053", "localidad": "SMT", "cuit": "30-85896356-9", "iva": "Exento", "concepto": "pago", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>0001-00000022</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>O.S. Del Personal Mosaista</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>19/08/2025</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000022", "fecha": "19/08/2025", "cliente": "O.S. Del Personal Mosaista", "domicilio": "Quirno 89", "localidad": "CABA", "cuit": "30-60658818-2", "iva": "Exento", "concepto": "Pago Factura 19875", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>0001-00000023</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Cofaral</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>19/08/2025</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000023", "fecha": "19/08/2025", "cliente": "Cofaral", "domicilio": "Catamarca 1053", "localidad": "SMT", "cuit": "30-85896356-9", "iva": "Exento", "concepto": "Pago factura 19865", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>0001-00000024</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Cofaral</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>19/08/2025</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000024", "fecha": "19/08/2025", "cliente": "Cofaral", "domicilio": "Catamarca 1053", "localidad": "SMT", "cuit": "30-85896356-9", "iva": "Exento", "concepto": "Pago Factura 19875", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>0001-00000025</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Cofaral</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>19/08/2025</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000025", "fecha": "19/08/2025", "cliente": "Cofaral", "domicilio": "Catamarca 1053", "localidad": "SMT", "cuit": "30-85896356-9", "iva": "Exento", "concepto": "Pago facturas", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>0001-00000026</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Cofaral</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>19/08/2025</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000026", "fecha": "19/08/2025", "cliente": "Cofaral", "domicilio": "Catamarca 1053", "localidad": "SMT", "cuit": "30-85896356-9", "iva": "Exento", "concepto": "Pago facturas", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>0001-00000027</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Cofaral</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>19/08/2025</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000027", "fecha": "19/08/2025", "cliente": "Cofaral", "domicilio": "Catamarca 1053", "localidad": "SMT", "cuit": "30-85896356-9", "iva": "Exento", "concepto": "PAgo", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>0001-00000028</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Cofaral</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>19/08/2025</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000028", "fecha": "19/08/2025", "cliente": "Cofaral", "domicilio": "Catamarca 1053", "localidad": "SMT", "cuit": "30-85896356-9", "iva": "Exento", "concepto": "PAgo", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>0001-00000029</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Cofaral</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>19/08/2025</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000029", "fecha": "19/08/2025", "cliente": "Cofaral", "domicilio": "Catamarca 1053", "localidad": "SMT", "cuit": "30-85896356-9", "iva": "Exento", "concepto": "Pago Factura 18956", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>0001-00000030</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Cofaral</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>19/08/2025</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000030", "fecha": "19/08/2025", "cliente": "Cofaral", "domicilio": "Catamarca 1053", "localidad": "SMT", "cuit": "30-85896356-9", "iva": "Exento", "concepto": "Pago Factura 19874", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>0001-00000031</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Cofaral</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>19/08/2025</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000031", "fecha": "19/08/2025", "cliente": "Cofaral", "domicilio": "Catamarca 1053", "localidad": "SMT", "cuit": "30-85896356-9", "iva": "Exento", "concepto": "Pago factura 19875", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>0001-00000032</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Cofaral</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>19/08/2025</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000032", "fecha": "19/08/2025", "cliente": "Cofaral", "domicilio": "Catamarca 1053", "localidad": "SMT", "cuit": "30-85896356-9", "iva": "Exento", "concepto": "Pago factura 19836", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>0001-00000033</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Cofaral</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>19/08/2025</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000033", "fecha": "19/08/2025", "cliente": "Cofaral", "domicilio": "Catamarca 1053", "localidad": "SMT", "cuit": "30-85896356-9", "iva": "Exento", "concepto": "Pago factura 19856", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>0001-00000034</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Cofaral</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>20/08/2025</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6908718</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000034", "fecha": "20/08/2025", "cliente": "Cofaral", "domicilio": "Catamarca 1053", "localidad": "SMT", "cuit": "30-85896356-9", "iva": "Exento", "concepto": "Pago Factura 19345", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 6908718.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>0001-00000036</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Cofaral</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>20/08/2025</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>7514650</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000036", "fecha": "20/08/2025", "cliente": "Cofaral", "domicilio": "Catamarca 1053", "localidad": "SMT", "cuit": "30-85896356-9", "iva": "Exento", "concepto": "Pago Factura 18956", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 7514650.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>0001-00000037</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Cofaral</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>20/08/2025</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>5125995.8</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000037", "fecha": "20/08/2025", "cliente": "Cofaral", "domicilio": "Catamarca 1053", "localidad": "SMT", "cuit": "30-85896356-9", "iva": "Exento", "concepto": "Pago Factura 19856", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 5125995.8}</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>0001-00000038</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Cofaral</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>20/08/2025</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>14651760.55</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000038", "fecha": "20/08/2025", "cliente": "Cofaral", "domicilio": "Catamarca 1053", "localidad": "SMT", "cuit": "30-85896356-9", "iva": "Exento", "concepto": "Pago Factura 19856", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 14651760.55}</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>0001-00000039</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Cofaral</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>20/08/2025</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6829936</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000039", "fecha": "20/08/2025", "cliente": "Cofaral", "domicilio": "Catamarca 1053", "localidad": "SMT", "cuit": "30-85896356-9", "iva": "Exento", "concepto": "Pago Factura 19875", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 6829936.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>0001-00000043</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>DR. Felipe S. Palazzo</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>20/08/2025</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>136586.25</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000043", "fecha": "20/08/2025", "cliente": "DR. Felipe S. Palazzo", "domicilio": "Sarmiento 157", "localidad": "San Miguel de Tucuman", "cuit": "20-22073820-6", "iva": "Responsable Inscripto", "concepto": "Pago Factura 19356", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 136586.25}</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>0001-00000044</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Ricardo C. Mora y CIA SRL</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>21/08/2025</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>1578406.05</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000044", "fecha": "21/08/2025", "cliente": "Ricardo C. Mora y CIA SRL", "domicilio": "9 De julio 68", "localidad": "San Miguel de Tucuman", "cuit": "30-71505876-2", "iva": "Responsable Inscripto", "concepto": "Pago Facturas 19359 / 19360", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1578406.05}</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>0001-00000064</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Hospital Avellaneda</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>22/08/2025</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>18423746.51</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000064", "fecha": "22/08/2025", "cliente": "Hospital Avellaneda", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-69182284-9", "iva": "Exento", "concepto": "Pago Facturas 25177 / 24929 / 24404 / 24706 / 24697 / 24705 / 24807 / 24707 / 24814", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 18423746.51}</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>0001-00000067</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>23/08/2025</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>5533389.96</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000067", "fecha": "23/08/2025", "cliente": "Ministerio de Salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago liquidaciones 497-2025 / 3212-2024", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 5533389.96}</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>0001-00000069</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Aliar S.A.</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>25/08/2025</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>5866665.4</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000069", "fecha": "25/08/2025", "cliente": "Aliar S.A.", "domicilio": "Maipu 70", "localidad": "San Miguel de Tucuman", "cuit": "30-70792118-4", "iva": "Responsable Inscripto", "concepto": "Pago Facturas 19227 / 19264", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 5866665.4}</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>0001-00000070</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Obra Social del Personal de la Industria Azucarera</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>25/08/2025</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>15008094</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000070", "fecha": "25/08/2025", "cliente": "Obra Social del Personal de la Industria Azucarera", "domicilio": "Congreso 348", "localidad": "San Miguel de Tucuman", "cuit": "30-62285904-8", "iva": "Exento", "concepto": "Pago Facturas 22720 / 22811 / 22833", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 15008094.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>0001-00000071</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>25/08/2025</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>16489556.5</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000071", "fecha": "25/08/2025", "cliente": "Ministerio de Salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago liquidacion 525-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 16489556.5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>0001-00000072</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>26/08/2025</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>5533389.96</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000072", "fecha": "26/08/2025", "cliente": "Ministerio de Salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago factura 497-2025 / 3214-2024", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 5533389.96}</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>0001-00000073</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>26/08/2025</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>16489556.5</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000073", "fecha": "26/08/2025", "cliente": "Ministerio de Salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago factura 525-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 16489556.5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>0001-00000074</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>26/08/2025</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>2120266.75</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000074", "fecha": "26/08/2025", "cliente": "Ministerio de Salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago factura 441-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 2120266.75}</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>0001-00000075</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>26/08/2025</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>4109176.56</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000075", "fecha": "26/08/2025", "cliente": "Ministerio de Salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago factura 414-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 4109176.56}</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>0001-00000076</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Hospital Nestor Kirchner</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>26/08/2025</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>120520</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000076", "fecha": "26/08/2025", "cliente": "Hospital Nestor Kirchner", "domicilio": "Mendoza 128", "localidad": "San Miguel de Tucuman", "cuit": "30-69182284-9", "iva": "Exento", "concepto": "Pago factura 25119", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 120520.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>0001-00000077</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Farmacia y Drog. Sudamericana</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>26/08/2025</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>317230</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000077", "fecha": "26/08/2025", "cliente": "Farmacia y Drog. Sudamericana", "domicilio": "Alberdi 102", "localidad": "Salta", "cuit": "30-56173408-5", "iva": "Responsable Inscripto", "concepto": "Pago factura 19026", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 317230.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>0001-00000078</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Farmacia y Drog. Sudamericana</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>26/08/2025</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>851951.55</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000078", "fecha": "26/08/2025", "cliente": "Farmacia y Drog. Sudamericana", "domicilio": "Alberdi 102", "localidad": "Salta", "cuit": "30-56173408-5", "iva": "Responsable Inscripto", "concepto": "Pago factura 19258", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 851951.55}</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>0001-00000079</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Farmacia y Drog. Sudamericana</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>26/08/2025</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>317230</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000079", "fecha": "26/08/2025", "cliente": "Farmacia y Drog. Sudamericana", "domicilio": "Alberdi 102", "localidad": "Salta", "cuit": "30-56173408-5", "iva": "Responsable Inscripto", "concepto": "Pago factura 19026", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 317230.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>0001-00000080</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Amsterdam Salud S.A</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>26/08/2025</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>16911.13</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000080", "fecha": "26/08/2025", "cliente": "Amsterdam Salud S.A", "domicilio": "Laprida 176 DPTO 1", "localidad": "San Miguel de Tucuman", "cuit": "30-70893009-8", "iva": "Responsable Inscripto", "concepto": "Pago factura 19361", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 16911.13}</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>0001-00000081</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>26/08/2025</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>4109176.56</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000081", "fecha": "26/08/2025", "cliente": "Ministerio de Salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago liquidacion 414-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 4109176.56}</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>0001-00000082</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>26/08/2025</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>1977847.58</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000082", "fecha": "26/08/2025", "cliente": "Ministerio de Salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago liquidacion 453-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1977847.58}</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>0001-00000083</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>26/08/2025</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>3878637.5</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000083", "fecha": "26/08/2025", "cliente": "Ministerio de Salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago liquidacion 570-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 3878637.5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>0001-00000084</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>26/08/2025</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>3576376.57</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000084", "fecha": "26/08/2025", "cliente": "Ministerio de Salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago liquidacion 599-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 3576376.57}</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>0001-00000085</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>26/08/2025</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>5471685.76</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000085", "fecha": "26/08/2025", "cliente": "Ministerio de Salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago liquidacion 575-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 5471685.76}</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>0001-00000086</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>26/08/2025</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>12270317.66</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000086", "fecha": "26/08/2025", "cliente": "Ministerio de Salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago liquidacion 478-2025 / 3198-2024", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 12270317.66}</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>0001-00000087</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>26/08/2025</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>1590656</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000087", "fecha": "26/08/2025", "cliente": "Ministerio de Salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago liquidacion 630-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1590656.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>0001-00000088</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>26/08/2025</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>214405.3</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000088", "fecha": "26/08/2025", "cliente": "Ministerio de Salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago liquidacion 610-2025 / 3333-2024", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 214405.3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>0001-00000089</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>26/08/2025</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>2695864.42</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000089", "fecha": "26/08/2025", "cliente": "Ministerio de Salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago liquidacion 3151-2024", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 2695864.42}</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>0001-00000090</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>26/08/2025</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>14643700.88</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000090", "fecha": "26/08/2025", "cliente": "Ministerio de Salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago liquidacion 577-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 14643700.88}</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>0001-00000091</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>26/08/2025</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>1329060.12</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000091", "fecha": "26/08/2025", "cliente": "Ministerio de Salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago liquidacion 3109-2024", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1329060.12}</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>0001-00000092</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>26/08/2025</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>2120266.75</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000092", "fecha": "26/08/2025", "cliente": "Ministerio de Salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago liquidacion 441-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 2120266.75}</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>0001-00000093</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>26/08/2025</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>5533389.96</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000093", "fecha": "26/08/2025", "cliente": "Ministerio de Salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago liquidacion 497-2025 / 3214-2024", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 5533389.96}</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>0001-00000094</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>26/08/2025</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>16489556.5</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000094", "fecha": "26/08/2025", "cliente": "Ministerio de Salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago liquidacion 525-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 16489556.5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>0001-00000095</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>26/08/2025</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>1977847.58</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000095", "fecha": "26/08/2025", "cliente": "Ministerio de Salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago liquidacion 453-2025 / 3168-2024", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1977847.58}</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>0001-00000096</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Farmacia Torres SRL</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>26/08/2025</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>5304.38</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000096", "fecha": "26/08/2025", "cliente": "Farmacia Torres SRL", "domicilio": "Uttinger 99", "localidad": "Tafi Viejo", "cuit": "30-71455367-0", "iva": "Responsable Inscripto", "concepto": "Pago Factura 19372", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 5304.38}</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>0001-00000097</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Dirreccion General de Programa Integrado de Salud</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>26/08/2025</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>972536.9</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000097", "fecha": "26/08/2025", "cliente": "Dirreccion General de Programa Integrado de Salud", "domicilio": "Las Piedras 626", "localidad": "San Miguel de Tucuman", "cuit": "30-69182284-9", "iva": "Exento", "concepto": "Pago Facturas 24042 / 24588 / 24589 / 24591 / 24590", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 972536.9}</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>0001-00000098</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Dirreccion General de Programa Integrado de Salud</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>26/08/2025</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>126609</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000098", "fecha": "26/08/2025", "cliente": "Dirreccion General de Programa Integrado de Salud", "domicilio": "Las Piedras 626", "localidad": "San Miguel de Tucuman", "cuit": "30-69182284-9", "iva": "Exento", "concepto": "Pago Facturas 23666", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 126609.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>0001-00000099</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>O.S. Del Personal Mosaista</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>27/08/2025</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>4300000</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000099", "fecha": "27/08/2025", "cliente": "O.S. Del Personal Mosaista", "domicilio": "Quirno 89", "localidad": "CABA", "cuit": "30-60658818-2", "iva": "Inscripto", "concepto": "Pago facturas 24097 ($432.870) / 24098($453.785) / 24182 ($1.950.000) / 24218 ($161.008) / 24227 ($1.302.337)", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 4300000.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>0001-00000100</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>O.S. Del Personal Mosaista</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>27/08/2025</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000100", "fecha": "27/08/2025", "cliente": "O.S. Del Personal Mosaista", "domicilio": "Quirno 89", "localidad": "CABA", "cuit": "30-60658818-2", "iva": "Inscripto", "concepto": "Pago facturas 23932 ($773.102) / 24084 ($87.382) / 24085 ($22.386) / 24097 ($1.517.130)", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 2400000.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>0001-00000101</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>O.S. Del Personal Mosaista</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>27/08/2025</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>2300000</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000101", "fecha": "27/08/2025", "cliente": "O.S. Del Personal Mosaista", "domicilio": "Quirno 89", "localidad": "CABA", "cuit": "30-60658818-2", "iva": "Inscripto", "concepto": "Pago Facturas 23676 ($4.947) / 23684 ($87.229) / 23690($20.532) / 23700($57477) / 23701($320.391) / 23706($5.258) / 23709($86.684) / 23711($5.993) /23722 ($57.477)/ 23723($10.266) / 23724($57.477) / 23725($161.206) / 23742($5.993) / 23749($23.310) / 23753($488.330) / 23816($5.592) / 23817($135.563) / 23831($58.176) / 23837($148.678) / 23851($51.030) / 23899($5.366) / 23917($4.947) / 23932($498.078)", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 2300000.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>0001-00000105</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>O.S. Del Personal Mosaista</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>27/08/2025</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>2300000</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000105", "fecha": "27/08/2025", "cliente": "O.S. Del Personal Mosaista", "domicilio": "Quirno 89", "localidad": "CABA", "cuit": "30-60658818-2", "iva": "Inscripto", "concepto": "Pago Facturas 23676 ($4.947) / 23684 ($87.229) / 23690($20.532) / 23700($57477) / 23701($320.391) /\n23706($5.258) / 23709($86.684) / 23711($5.993) / 23722($57.477) / 23723($10.266) / 23724($57.477) /\n23725($161.206) / 23742($5.993) / 23749($23.310) / 23753 ($488.330) / 23816($5.592) / 23817($135.563) /\n23831($58.176) / 23837($148.678) / 23851($51.030) / 23899($5.366) / 23917 ($4.947) / 23932($498.078)", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 2300000.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>0001-00000106</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>O.S. Del Personal Mosaista</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>27/08/2025</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>482820</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000106", "fecha": "27/08/2025", "cliente": "O.S. Del Personal Mosaista", "domicilio": "Quirno 89", "localidad": "CABA", "cuit": "30-60658818-2", "iva": "Inscripto", "concepto": "Pago Facturas 23553($196.845) / 23558($5.468) / 23560 ($57.477) / 23563 ($5.993) / 23645 ($5.993) / 23656\n($56.200) / 23657 ($153.798) / 23676 (1.046)", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 482820.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>0001-00000108</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>O.S. Del Personal Mosaista</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>27/08/2025</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>15100000</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000108", "fecha": "27/08/2025", "cliente": "O.S. Del Personal Mosaista", "domicilio": "Quirno 89", "localidad": "CABA", "cuit": "30-60658818-2", "iva": "Inscripto", "concepto": "Pago Facturas 21816($7.035.128)/ 22462($185942) / 22537($781.633) / 22554($344059) / 22584($4.354.400) / 22596($275.350) /\n22698($22.194) / 22711($459.251) / 22743($305.344) / 22850($5.141) / 22863($5.468) / 22987($65.405) / 22992($447.190) /\n22993($54.722) / 22995($105…", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 15100000.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>0001-00000111</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>O.S. Del Personal Mosaista</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>27/08/2025</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>15100000</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000111", "fecha": "27/08/2025", "cliente": "O.S. Del Personal Mosaista", "domicilio": "Quirno 89", "localidad": "CABA", "cuit": "30-60658818-2", "iva": "Inscripto", "concepto": "Pago Facturas 21816($7.035.128)/ 22462($185942) / 22537($781.633) / 22554($344059) / 22584($4.354.400) / 22596($275.350) /\n22698($22.194) / 22711($459.251) / 22743($305.344) / 22850($5.141) / 22863($5.468) / 22987($65.405) / 22992($447.190) /\n22993($54.722) / 22995($105.377) / 22996($105.377) / 22999($54.722) / 23002($5.468) / 23134($54.722) / 23141($69.124) /\n23309($5.859) / 23340($5.859) / 23340($5.859) / 23366($5.468) / 23366($5.468) / 23464($4.745) / 23466($4.745) / 23545($5.859) / 2354…", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 15100000.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>0001-00000112</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>O.S. Del personal Mosaista</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>27/08/2025</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>15100000</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000112", "fecha": "27/08/2025", "cliente": "O.S. Del personal Mosaista", "domicilio": "Quirno 89", "localidad": "CABA", "cuit": "30-60658818-2", "iva": "Inscripto", "concepto": "Pago Facturas 21816($7.035.128)/ 22462($185942) / 22537($781.633) / 22554($344059) / 22584($4.354.400) / 22596($275.350) /\n22698($22.194) / 22711($459.251) / 22743($305.344) / 22850($5.141) / 22863($5.468) / 22987($65.405) / 22992($447.190) /\n22993($54.722) / 22995($105.377) / 22996($105.377) / 22999($54.722) / 23002($5.468) / 23134($54.722) / 23141($69.124) /\n23309($5.859) / 23340($5.859) / 23340($5.859) / 23366($5.468) / 23366($5.468) / 23464($4.745) / 23466($4.745) / 23545($5.859) / 2354…", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 15100000.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>0001-00000113</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>O.S. Del personal Mosaista</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>27/08/2025</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>4310000</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000113", "fecha": "27/08/2025", "cliente": "O.S. Del personal Mosaista", "domicilio": "Quirno 89", "localidad": "CABA", "cuit": "30-60658818-2", "iva": "Inscripto", "concepto": "Pago Facturas 24227($1.764.987) / 24232($48.966) / 24270($5.473) / 24286($56.531) / 24315($5.638) /\n24367($440.433) / 24379($9.337) / 24380($139.091) / 24381($139.091) / 24442($440.433) / 24476($1.315.672)\n/ 24481($5.638) / 24552($46.725) / 24555($5.638) / 24556($14.970) / 24652($5.638)", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 4310000.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>0001-00000114</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Hospital Centro de Salud</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>28/08/2025</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>12298450</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000114", "fecha": "28/08/2025", "cliente": "Hospital Centro de Salud", "domicilio": "Av. Avellaneda 750", "localidad": "San Miguel de Tucuman", "cuit": "30691822849", "iva": "Exento", "concepto": "Pago Factura 24816", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 12298450.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>0001-00000115</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Farmacia Guadalupe De Aragon Natalia Ter</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>28/08/2025</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>137448</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000115", "fecha": "28/08/2025", "cliente": "Farmacia Guadalupe De Aragon Natalia Ter", "domicilio": "Ruta 306 KM Leales", "localidad": "Leales", "cuit": "27-26783241-8", "iva": "Responsable Inscripto", "concepto": "Pago Factura 19379", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 137448.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>0001-00000116</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>O.S. Del Personal Mosaista</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>28/08/2025</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>15100000</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000116", "fecha": "28/08/2025", "cliente": "O.S. Del Personal Mosaista", "domicilio": "Quirno 89", "localidad": "CABA", "cuit": "30-60658818-2", "iva": "Inscripto", "concepto": "Pago Facturas 21816($7.035.128)/ 22462($185942) / 22537($781.633) / 22554($344059) / 22584($4.354.400) /\n22596($275.350) / 22698($22.194) / 22711($459.251) / 22743($305.344) / 22850($5.141) / 22863($5.468) /\n22987($65.405) / 22992($447.190) / 22993($54.722) / 22995($105.377) / 22996($105.377) / 22999($54.722) /\n23002($5.468) / 23134($54.722) / 23141($69.124) / 23309($5.859) / 23340($5.859) / 23340($5.859) /\n23366($5.468) / 23366($5.468) / 23464($4.745) / 23466($4.745) / 23545($5.859) / 23546($223.868) /\n23547($4.818) / 23550($64.354) / 23551($5.468) / 23553($83.595)", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 15100000.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>0001-00000117</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Hospital Regional</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>28/08/2025</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>1807800</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000117", "fecha": "28/08/2025", "cliente": "Hospital Regional", "domicilio": "San Luis 150", "localidad": "Concepcion", "cuit": "30-69182284-9", "iva": "Exento", "concepto": "Pago facturas 24810", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1807800.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>0001-00000118</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Hospital Regional</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>29/08/2025</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>1807800</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000118", "fecha": "29/08/2025", "cliente": "Hospital Regional", "domicilio": "San Luis 150", "localidad": "Concepcion", "cuit": "30-69182284-9", "iva": "Exento", "concepto": "Pago Factura 25112", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1807800.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>0001-00000119</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Obra Social del Personal Prensa</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>29/08/2025</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>1300894</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000119", "fecha": "29/08/2025", "cliente": "Obra Social del Personal Prensa", "domicilio": "Junin 775", "localidad": "San Miguel de Tucuman", "cuit": "30-67540406-9", "iva": "Exento", "concepto": "Pago Facturas 24359 / 25105 / 25106 / 24141", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1300894.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>0001-00000120</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Hospital Padilla</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>29/08/2025</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>4775100</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000120", "fecha": "29/08/2025", "cliente": "Hospital Padilla", "domicilio": "Alberdi 550", "localidad": "San Miguel de Tucuman", "cuit": "30-69182284-9", "iva": "Exento", "concepto": "Pago Facturas 24806", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 4775100.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>0001-00000121</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Fcia Universidad</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>29/08/2025</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>18546140.66</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000121", "fecha": "29/08/2025", "cliente": "Fcia Universidad", "domicilio": "San Martin 864", "localidad": "San Miguel de Tucuman", "cuit": "30-54667048-8", "iva": "Exento", "concepto": "Pago Facturas 19210 / 19214 / 19216 / 19217 / 19228 / 19233 / 19234 / 19243 / 19244 / 19277 / 19279 / 19280 /\n19301", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 18546140.66}</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>0001-00000122</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Obra Social Del Personal Prensa</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>30/08/2025</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>1300894</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000122", "fecha": "30/08/2025", "cliente": "Obra Social Del Personal Prensa", "domicilio": "Junin 775", "localidad": "San Miguel de Tucuman", "cuit": "30-67540406-9", "iva": "Exento", "concepto": "Pago Facturas 24359 / 25105 / 25106 / 25141", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1300894.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>0001-00000123</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE PROGRAMA INTEGRADO DE SALUD</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>01/09/2025</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>28199688.8</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000123", "fecha": "01/09/2025", "cliente": "DIRECCION GENERAL DE PROGRAMA INTEGRADO DE SALUD", "domicilio": "Las Piedras 626", "localidad": "San Miguel de Tucuman", "cuit": "30-69182284-9", "iva": "Exento", "concepto": "Pago Factura 23809", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 28199688.8}</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>0001-00000124</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Farmacia Nueva</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>01/09/2025</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>56504.15</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000124", "fecha": "01/09/2025", "cliente": "Farmacia Nueva", "domicilio": "Lavalle 999", "localidad": "San Miguel De Tucuman", "cuit": "27-29917697-0", "iva": "Responsable Inscripto", "concepto": "Pago Factura 19384", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 56504.15}</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>0001-00000125</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE PROGRAMA INTEGRADO DE SALUD</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>01/09/2025</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>28199688.8</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000125", "fecha": "01/09/2025", "cliente": "DIRECCION GENERAL DE PROGRAMA INTEGRADO DE SALUD", "domicilio": "Las Piedras 626", "localidad": "San Miguel De Tucuman", "cuit": "30-69182284-9", "iva": "Exento", "concepto": "Pago Factura 23809.\nTransferencia $7.226.391,68 pendiente a realizar", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 28199688.8}</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>0001-00000126</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Bradel Del Pueblo</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>02/09/2025</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>11093561.35</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000126", "fecha": "02/09/2025", "cliente": "Bradel Del Pueblo", "domicilio": "Av. Alem 199", "localidad": "San Miguel de Tucuman", "cuit": "33-70241330-9", "iva": "Responsable Inscripto", "concepto": "Pago Factura 19276", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 11093561.35}</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>0001-00000127</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Cofaral</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>02/09/2025</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>3722144.08</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000127", "fecha": "02/09/2025", "cliente": "Cofaral", "domicilio": "Catamarca 1053", "localidad": "SMT", "cuit": "30-85896356-9", "iva": "Responsable Inscripto", "concepto": "Pago Factura 19318 / 19325 / NDE 26-53 ($4.640.72) / NDE 26-54 ($25.136.43)", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 3722144.08}</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>0001-00000128</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Obra Social de Conductores Camioneros</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>02/09/2025</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>27043315</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000128", "fecha": "02/09/2025", "cliente": "Obra Social de Conductores Camioneros", "domicilio": "Catamarca 841", "localidad": "San Miguel de Tucuman", "cuit": "30-66150769-8", "iva": "Exento", "concepto": "Pago facturas a detallar", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 27043315.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>0001-00000129</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>03/09/2025</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>13048266.71</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000129", "fecha": "03/09/2025", "cliente": "Ministerio de Salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago Liquidacion 768-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 13048266.71}</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>0001-00000130</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>03/09/2025</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>3428789.62</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000130", "fecha": "03/09/2025", "cliente": "Ministerio de Salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago Liquidacion 709-2025 / 3365-2024", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 3428789.62}</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>0001-00000131</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>BRAMED</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>03/09/2025</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>2772229.25</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000131", "fecha": "03/09/2025", "cliente": "BRAMED", "domicilio": "Monteagudo y Marcos Paz", "localidad": "San Miguel de Tucuman", "cuit": "30-71073853-6", "iva": "Responsable Inscripto", "concepto": "Pago factura 19039 / 19059 / 19061 / 19062", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 2772229.25}</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>0001-00000132</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>BRAMED</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>03/09/2025</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>910703.89</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000132", "fecha": "03/09/2025", "cliente": "BRAMED", "domicilio": "Monteagudo y Marcos Paz", "localidad": "San Miguel de Tucuman", "cuit": "30-71073853-6", "iva": "Responsable Inscripto", "concepto": "Pago factura 19127 / 19130 / 19166 / 19167 / 19173", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 910703.89}</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>0001-00000133</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>OSFATUN</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>04/09/2025</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>439991</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000133", "fecha": "04/09/2025", "cliente": "OSFATUN", "domicilio": "Rep Bolivariana de Venezuela 3264", "localidad": "San Miguel de Tucuman", "cuit": "30-68333676-5", "iva": "Responsable Inscripto", "concepto": "Pago factura 19388", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 439991.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>0001-00000134</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>04/09/2025</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>8114153.69</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000134", "fecha": "04/09/2025", "cliente": "Ministerio de Salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Responsable Inscripto", "concepto": "Pago liquidacion 787-2025 / 3433-2024", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 8114153.69}</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>0001-00000135</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>04/09/2025</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>6441968.77</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000135", "fecha": "04/09/2025", "cliente": "Ministerio de Salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Responsable Inscripto", "concepto": "Pago liquidacion 743-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 6441968.77}</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>0001-00000136</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Farmacia Nueva</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>04/09/2025</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>394251.9</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000136", "fecha": "04/09/2025", "cliente": "Farmacia Nueva", "domicilio": "Lavalle 999", "localidad": "San Miguel de Tucuman", "cuit": "27-29917697-0", "iva": "Responsable Inscripto", "concepto": "Pago liquidacion 743-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 394251.9}</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>0001-00000137</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Inst. de Prev. y Seg. Social de la Prov</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>04/09/2025</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>398804734.92</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000137", "fecha": "04/09/2025", "cliente": "Inst. de Prev. y Seg. Social de la Prov", "domicilio": "Las Piedras 530", "localidad": "San Miguel de Tucuman", "cuit": "30-63394922-7", "iva": "Exento", "concepto": "Pago Factura 24388 / 24389 / 24390 / 24391 / 24392 / NCR B-2-706 ($2.203.832,06) / NCR x Desc NOVO\n(-$9.153.273,13) / NCR x Pronto Pago (-$29.599.084,61) / NCR x Freestyle (-$9.526.215,07)", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 398804734.92}</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>0001-00000138</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Inst. de Prev. y Seg. Social de la Prov</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>04/09/2025</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>398804734.92</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000138", "fecha": "04/09/2025", "cliente": "Inst. de Prev. y Seg. Social de la Prov", "domicilio": "Las Piedras 530", "localidad": "San Miguel de Tucuman", "cuit": "30-63394922-7", "iva": "Exento", "concepto": "Pago Factura 24388 / 24389 / 24390 / 24391 / 24392 / NCR B-2-706 ($2.203.832,06) / NCR x Desc NOVO\n(-$9.153.273,13) / NCR x Pronto Pago (-$29.599.084,61) / NCR x Freestyle (-$9.526.215,07)", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 398804734.92}</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>0001-00000139</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Inst. de Prev. y Seg. Social de la Prov</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>04/09/2025</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>398804734.92</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000139", "fecha": "04/09/2025", "cliente": "Inst. de Prev. y Seg. Social de la Prov", "domicilio": "Las Piedras 530", "localidad": "San Miguel de Tucuman", "cuit": "30-63394922-7", "iva": "Exento", "concepto": "Pago Factura 24388 / 24389 / 24390 / 24391 / 24392 / NCR B-2-706 ($2.203.832,06) / NCR x Desc NOVO\n(-$9.153.273,13) / NCR x Pronto Pago (-$29.599.084,61) / NCR x Freestyle (-$9.526.215,07)", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 398804734.92}</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>0001-00000140</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Farmacia Nueva</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>05/09/2025</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>394251.9</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000140", "fecha": "05/09/2025", "cliente": "Farmacia Nueva", "domicilio": "Lavalle 999", "localidad": "San Miguel de Tucuman", "cuit": "27-29917697-0", "iva": "Responsable Inscripto", "concepto": "Pago Factura 19396", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 394251.9}</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>0001-00000141</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Hospital Eva Peron</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>05/09/2025</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>1807800</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000141", "fecha": "05/09/2025", "cliente": "Hospital Eva Peron", "domicilio": "Ruta 9 y Calle El Carmen 1", "localidad": "Banda Del Rio Sali", "cuit": "30-69182284-9", "iva": "Responsable Inscripto", "concepto": "Pago Factura 25115", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1807800.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>0001-00000142</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Farmacia Del Jardin</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>05/09/2025</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>24710.63</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000142", "fecha": "05/09/2025", "cliente": "Farmacia Del Jardin", "domicilio": "Av. Siria 1305", "localidad": "San Miguel De Tucuman", "cuit": "20-21328047-4", "iva": "Responsable Inscripto", "concepto": "Pago Factura 19401", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 24710.63}</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>0001-00000143</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Drogueria Distribuidora Norte</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>05/09/2025</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>2348836.73</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000143", "fecha": "05/09/2025", "cliente": "Drogueria Distribuidora Norte", "domicilio": "Catamarca 24", "localidad": "San Miguel De Tucuman", "cuit": "20-16132777-9", "iva": "Responsable Inscripto", "concepto": "Pago Factura 19397", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 2348836.73}</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>0001-00000144</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Soremer</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>05/09/2025</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>43995</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000144", "fecha": "05/09/2025", "cliente": "Soremer", "domicilio": "Monteagudo 815", "localidad": "San Miguel De Tucuman", "cuit": "30-64058584-2", "iva": "Responsable Inscripto", "concepto": "Pago Factura 19387", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 43995.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>0001-00000145</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Dr. Felipe Palazzo</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>05/09/2025</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>5028.08</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000145", "fecha": "05/09/2025", "cliente": "Dr. Felipe Palazzo", "domicilio": "Sarmiento 157", "localidad": "San Miguel De Tucuman", "cuit": "20-22073820-6", "iva": "Responsable Inscripto", "concepto": "Pago Factura 19405", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 5028.08}</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>0001-00000146</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Farmacia Nueva</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>06/09/2025</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>394251.9</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000146", "fecha": "06/09/2025", "cliente": "Farmacia Nueva", "domicilio": "Lavalle 999", "localidad": "San Miguel de Tucuman", "cuit": "27-29917697-0", "iva": "Responsable Inscripto", "concepto": "Pago Factura 19396", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 394251.9}</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>0001-00000147</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Infectologia Musa</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>06/09/2025</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>2563589.15</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000147", "fecha": "06/09/2025", "cliente": "Infectologia Musa", "domicilio": "Rondeau 887", "localidad": "San Miguel de Tucuman", "cuit": "30-71649808-1", "iva": "Responsable Inscripto", "concepto": "Pago Facturas 18848 / 19195 / 19261 / 19340", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 2563589.15}</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>0001-00000148</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Farmacia Del Jardin</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>08/09/2025</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>139124.7</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000148", "fecha": "08/09/2025", "cliente": "Farmacia Del Jardin", "domicilio": "Av. Siria 1305", "localidad": "San Miguel De Tucuman", "cuit": "20-21328047-4", "iva": "Responsable Inscripto", "concepto": "Pago factura 19406", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 139124.7}</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>0001-00000149</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Drog. Distribuidora Norte</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>08/09/2025</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>2348836.73</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000149", "fecha": "08/09/2025", "cliente": "Drog. Distribuidora Norte", "domicilio": "Catamarca 24", "localidad": "San Miguel De Tucuman", "cuit": "20-16134777-9", "iva": "Responsable Inscripto", "concepto": "Pago factura 19397", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 2348836.73}</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>0001-00000150</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>DR. Felipe Pallazo</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>08/09/2025</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>4860</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000150", "fecha": "08/09/2025", "cliente": "DR. Felipe Pallazo", "domicilio": "Sarmiento 157", "localidad": "San Miguel De Tucuman", "cuit": "20-22073820-6", "iva": "Responsable Inscripto", "concepto": "Pago factura 19408", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 4860.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>0001-00000151</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>DR. Felipe Palazzo</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>08/09/2025</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>4860</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000151", "fecha": "08/09/2025", "cliente": "DR. Felipe Palazzo", "domicilio": "Sarmiento 157", "localidad": "San Miguel De Tucuman", "cuit": "20-22073820-6", "iva": "Responsable Inscripto", "concepto": "Pago factura 19408", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 4860.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>0001-00000152</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Hospital Padilla</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>08/09/2025</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>903900</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000152", "fecha": "08/09/2025", "cliente": "Hospital Padilla", "domicilio": "Alberdi 550", "localidad": "San Miguel De Tucuman", "cuit": "30-69182284-9", "iva": "Exento", "concepto": "Pago factura 24804", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 903900.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>0001-00000153</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Farmacia Nueva</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>08/09/2025</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>56504.15</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000153", "fecha": "08/09/2025", "cliente": "Farmacia Nueva", "domicilio": "Lavalle 999", "localidad": "San Miguel De Tucuman", "cuit": "27-29917697-0", "iva": "Responsable Inscripto", "concepto": "Pago factura 19410", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 56504.15}</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>0001-00000154</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Hospital Lamadrid</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>1043100</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000154", "fecha": "09/09/2025", "cliente": "Hospital Lamadrid", "domicilio": "Sarmiento 453", "localidad": "Monteros", "cuit": "30-69182284-9", "iva": "Exento", "concepto": "Pago Factura 25246 / 25382", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1043100.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>0001-00000155</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Mutual de la Asoc. Bancaria SMT</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>301100</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000155", "fecha": "09/09/2025", "cliente": "Mutual de la Asoc. Bancaria SMT", "domicilio": "San Martin 469", "localidad": "San Miguel de Tucuman", "cuit": "30-65479852-0", "iva": "Exento", "concepto": "Pago Factura 25832", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 301100.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>0001-00000156</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Obra Social de Conductores Camioneros</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>932438</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000156", "fecha": "09/09/2025", "cliente": "Obra Social de Conductores Camioneros", "domicilio": "Catamarca 841", "localidad": "San Miguel de Tucuman", "cuit": "30-66150769-8", "iva": "Exento", "concepto": "Pago Factura 25567", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 932438.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>0001-00000157</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Obra Social de Conductores Camioneros</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>932438</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000157", "fecha": "09/09/2025", "cliente": "Obra Social de Conductores Camioneros", "domicilio": "Catamarca 841", "localidad": "San Miguel de Tucuman", "cuit": "30-66150769-8", "iva": "Exento", "concepto": "Pago Factura 25567", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 932438.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>0001-00000158</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Obra Social de Conductores Camioneros</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>697103</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000158", "fecha": "09/09/2025", "cliente": "Obra Social de Conductores Camioneros", "domicilio": "Catamarca 841", "localidad": "San Miguel de Tucuman", "cuit": "30-66150769-8", "iva": "Exento", "concepto": "Pago Factura 25404", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 697103.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>0001-00000159</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Obra Social de Conductores Camioneros</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>697103</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000159", "fecha": "09/09/2025", "cliente": "Obra Social de Conductores Camioneros", "domicilio": "Catamarca 841", "localidad": "San Miguel de Tucuman", "cuit": "30-66150769-8", "iva": "Exento", "concepto": "Pago Factura 25402", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 697103.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>0001-00000160</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Obra Social de Conductores Camioneros</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>1762251</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000160", "fecha": "09/09/2025", "cliente": "Obra Social de Conductores Camioneros", "domicilio": "Catamarca 841", "localidad": "San Miguel de Tucuman", "cuit": "30-66150769-8", "iva": "Exento", "concepto": "Pago Factura 25402", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1762251.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>0001-00000161</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Obra Social de Conductores Camioneros</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>697103</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000161", "fecha": "09/09/2025", "cliente": "Obra Social de Conductores Camioneros", "domicilio": "Catamarca 841", "localidad": "San Miguel de Tucuman", "cuit": "30-66150769-8", "iva": "Exento", "concepto": "Pago Factura 25403", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 697103.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>0001-00000162</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Obra Social de Conductores Camioneros</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>9676</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000162", "fecha": "09/09/2025", "cliente": "Obra Social de Conductores Camioneros", "domicilio": "Catamarca 841", "localidad": "San Miguel de Tucuman", "cuit": "30-66150769-8", "iva": "Exento", "concepto": "Pago Factura 25483", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 9676.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>0001-00000163</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Obra Social de Conductores Camioneros</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>1762251</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000163", "fecha": "09/09/2025", "cliente": "Obra Social de Conductores Camioneros", "domicilio": "Catamarca 841", "localidad": "San Miguel de Tucuman", "cuit": "30-66150769-8", "iva": "Exento", "concepto": "Pago Factura 25511", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1762251.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>0001-00000164</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Obra Social de Conductores Camioneros</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>432658</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000164", "fecha": "09/09/2025", "cliente": "Obra Social de Conductores Camioneros", "domicilio": "Catamarca 841", "localidad": "San Miguel de Tucuman", "cuit": "30-66150769-8", "iva": "Exento", "concepto": "Pago Factura 25515", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 432658.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>0001-00000165</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Obra Social de Conductores Camioneros</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>432658</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000165", "fecha": "09/09/2025", "cliente": "Obra Social de Conductores Camioneros", "domicilio": "Catamarca 841", "localidad": "San Miguel de Tucuman", "cuit": "30-66150769-8", "iva": "Exento", "concepto": "Pago Factura 25514", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 432658.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>0001-00000166</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Obra Social de Conductores Camioneros</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>191440</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000166", "fecha": "09/09/2025", "cliente": "Obra Social de Conductores Camioneros", "domicilio": "Catamarca 841", "localidad": "San Miguel de Tucuman", "cuit": "30-66150769-8", "iva": "Exento", "concepto": "Pago Factura 24958", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 191440.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>0001-00000167</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Obra Social de Conductores Camioneros</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>14514</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000167", "fecha": "09/09/2025", "cliente": "Obra Social de Conductores Camioneros", "domicilio": "Catamarca 841", "localidad": "San Miguel de Tucuman", "cuit": "30-66150769-8", "iva": "Exento", "concepto": "Pago Factura 25559", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 14514.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>0001-00000168</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Obra Social de Conductores Camioneros</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>1786922</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000168", "fecha": "09/09/2025", "cliente": "Obra Social de Conductores Camioneros", "domicilio": "Catamarca 841", "localidad": "San Miguel de Tucuman", "cuit": "30-66150769-8", "iva": "Exento", "concepto": "Pago Factura 25562", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1786922.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>0001-00000169</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Obra Social de Conductores Camioneros</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>180341</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000169", "fecha": "09/09/2025", "cliente": "Obra Social de Conductores Camioneros", "domicilio": "Catamarca 841", "localidad": "San Miguel de Tucuman", "cuit": "30-66150769-8", "iva": "Exento", "concepto": "Pago Factura 25661", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 180341.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>0001-00000170</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Obra Social de Conductores Camioneros</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>1986339</v>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000170", "fecha": "09/09/2025", "cliente": "Obra Social de Conductores Camioneros", "domicilio": "Catamarca 841", "localidad": "San Miguel de Tucuman", "cuit": "30-66150769-8", "iva": "Exento", "concepto": "Pago Factura 24715", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1986339.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>0001-00000171</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Obra Social de Conductores Camioneros</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>487675</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000171", "fecha": "09/09/2025", "cliente": "Obra Social de Conductores Camioneros", "domicilio": "Catamarca 841", "localidad": "San Miguel de Tucuman", "cuit": "30-66150769-8", "iva": "Exento", "concepto": "Pago Factura 24775", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 487675.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>0001-00000172</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Obra Social de Conductores Camioneros</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>46020</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000172", "fecha": "09/09/2025", "cliente": "Obra Social de Conductores Camioneros", "domicilio": "Catamarca 841", "localidad": "San Miguel de Tucuman", "cuit": "30-66150769-8", "iva": "Exento", "concepto": "Pago Factura 25033", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 46020.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>0001-00000173</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Obra Social de Conductores Camioneros</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>2433204</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000173", "fecha": "09/09/2025", "cliente": "Obra Social de Conductores Camioneros", "domicilio": "Catamarca 841", "localidad": "San Miguel de Tucuman", "cuit": "30-66150769-8", "iva": "Exento", "concepto": "Pago Factura 25138", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 2433204.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>0001-00000174</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Obra Social de Conductores Camioneros</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>683435</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000174", "fecha": "09/09/2025", "cliente": "Obra Social de Conductores Camioneros", "domicilio": "Catamarca 841", "localidad": "San Miguel de Tucuman", "cuit": "30-66150769-8", "iva": "Exento", "concepto": "Pago Factura 25129", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 683435.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>0001-00000175</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Obra Social de Conductores Camioneros</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>426264</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000175", "fecha": "09/09/2025", "cliente": "Obra Social de Conductores Camioneros", "domicilio": "Catamarca 841", "localidad": "San Miguel de Tucuman", "cuit": "30-66150769-8", "iva": "Exento", "concepto": "Pago Factura 25185", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 426264.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>0001-00000176</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Obra Social de Conductores Camioneros</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>426264</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000176", "fecha": "09/09/2025", "cliente": "Obra Social de Conductores Camioneros", "domicilio": "Catamarca 841", "localidad": "San Miguel de Tucuman", "cuit": "30-66150769-8", "iva": "Exento", "concepto": "Pago Factura 25182", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 426264.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>0001-00000177</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Obra Social de Conductores Camioneros</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>683435</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000177", "fecha": "09/09/2025", "cliente": "Obra Social de Conductores Camioneros", "domicilio": "Catamarca 841", "localidad": "San Miguel de Tucuman", "cuit": "30-66150769-8", "iva": "Exento", "concepto": "Pago Factura 25184", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 683435.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>0001-00000178</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Obra Social de Conductores Camioneros</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>1762251</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000178", "fecha": "09/09/2025", "cliente": "Obra Social de Conductores Camioneros", "domicilio": "Catamarca 841", "localidad": "San Miguel de Tucuman", "cuit": "30-66150769-8", "iva": "Exento", "concepto": "Pago Factura 25213", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1762251.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>0001-00000179</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Obra Social de Conductores Camioneros</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>649666</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000179", "fecha": "09/09/2025", "cliente": "Obra Social de Conductores Camioneros", "domicilio": "Catamarca 841", "localidad": "San Miguel de Tucuman", "cuit": "30-66150769-8", "iva": "Exento", "concepto": "Pago Factura 25247", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 649666.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>0001-00000180</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Obra Social de Conductores Camioneros</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>122212</v>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000180", "fecha": "09/09/2025", "cliente": "Obra Social de Conductores Camioneros", "domicilio": "Catamarca 841", "localidad": "San Miguel de Tucuman", "cuit": "30-66150769-8", "iva": "Exento", "concepto": "Pago Factura 25281", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 122212.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>0001-00000181</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Obra Social de Conductores Camioneros</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>180341</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000181", "fecha": "09/09/2025", "cliente": "Obra Social de Conductores Camioneros", "domicilio": "Catamarca 841", "localidad": "San Miguel de Tucuman", "cuit": "30-66150769-8", "iva": "Exento", "concepto": "Pago Factura 25288", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 180341.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>0001-00000182</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Obra Social de Conductores Camioneros</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>2565395</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000182", "fecha": "09/09/2025", "cliente": "Obra Social de Conductores Camioneros", "domicilio": "Catamarca 841", "localidad": "San Miguel de Tucuman", "cuit": "30-66150769-8", "iva": "Exento", "concepto": "Pago Factura 25395", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 2565395.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>0001-00000183</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Obra Social de Conductores Camioneros</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>56176</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000183", "fecha": "09/09/2025", "cliente": "Obra Social de Conductores Camioneros", "domicilio": "Catamarca 841", "localidad": "San Miguel de Tucuman", "cuit": "30-66150769-8", "iva": "Exento", "concepto": "Pago Factura 25394", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 56176.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>0001-00000184</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Obra Social de Conductores Camioneros</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>2469702</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000184", "fecha": "09/09/2025", "cliente": "Obra Social de Conductores Camioneros", "domicilio": "Catamarca 841", "localidad": "San Miguel de Tucuman", "cuit": "30-66150769-8", "iva": "Exento", "concepto": "Pago Factura 25303", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 2469702.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>0001-00000185</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Obra Social de Conductores Camioneros</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>116876</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000185", "fecha": "09/09/2025", "cliente": "Obra Social de Conductores Camioneros", "domicilio": "Catamarca 841", "localidad": "San Miguel de Tucuman", "cuit": "30-66150769-8", "iva": "Exento", "concepto": "Pago Factura 25294", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 116876.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>0001-00000186</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Obra Social de Conductores Camioneros</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>2859076</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000186", "fecha": "09/09/2025", "cliente": "Obra Social de Conductores Camioneros", "domicilio": "Catamarca 841", "localidad": "San Miguel de Tucuman", "cuit": "30-66150769-8", "iva": "Exento", "concepto": "Pago Factura 25299", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 2859076.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>0001-00000187</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Obra Social de Conductores Camioneros</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>56176</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000187", "fecha": "09/09/2025", "cliente": "Obra Social de Conductores Camioneros", "domicilio": "Catamarca 841", "localidad": "San Miguel de Tucuman", "cuit": "30-66150769-8", "iva": "Exento", "concepto": "Pago Factura 25331", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 56176.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>0001-00000188</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Obra Social de Conductores Camioneros</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>122383</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000188", "fecha": "09/09/2025", "cliente": "Obra Social de Conductores Camioneros", "domicilio": "Catamarca 841", "localidad": "San Miguel de Tucuman", "cuit": "30-66150769-8", "iva": "Exento", "concepto": "Pago Factura 25579", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 122383.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>0001-00000189</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Dr. Felipe S. Palazzo</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>10/09/2025</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>5028.08</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000189", "fecha": "10/09/2025", "cliente": "Dr. Felipe S. Palazzo", "domicilio": "Sarmiento 157", "localidad": "San Miguel de Tucuman", "cuit": "20-22073820-6", "iva": "Responsable Inscripto", "concepto": "Pago Factura 19417", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 5028.08}</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>0001-00000190</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Obra Social</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>10/09/2025</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>41760</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000190", "fecha": "10/09/2025", "cliente": "Obra Social", "domicilio": "Sarmiento 157", "localidad": "San Miguel de Tucuman", "cuit": "20-22073820-6", "iva": "Responsable Inscripto", "concepto": "Pago Factura 25341", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 41760.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>0001-00000191</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Obra Social del Personal Prensa</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>10/09/2025</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>41760</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000191", "fecha": "10/09/2025", "cliente": "Obra Social del Personal Prensa", "domicilio": "Junin 775", "localidad": "San Miguel de Tucuman", "cuit": "30-67540406-9", "iva": "Responsable Inscripto", "concepto": "Pago Factura 25341", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 41760.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>0001-00000192</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Farmacia Raul Cainzo IPSST</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>10/09/2025</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>43933502.7</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000192", "fecha": "10/09/2025", "cliente": "Farmacia Raul Cainzo IPSST", "domicilio": "Las Piedras 530", "localidad": "San Miguel de Tucuman", "cuit": "30-63394922-7", "iva": "Exento", "concepto": "Pago Factura 25079 / 25080", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 43933502.7}</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>0001-00000193</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE PROGRAMA INTEGRADO DE SALUD</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>11/09/2025</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>28199688.8</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000193", "fecha": "11/09/2025", "cliente": "DIRECCION GENERAL DE PROGRAMA INTEGRADO DE SALUD", "domicilio": "Las Piedras 626", "localidad": "San Miguel de Tucuman", "cuit": "30-69182284-9", "iva": "Exento", "concepto": "Pago Factura 23809", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 28199688.8}</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>0001-00000194</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Sanatorio Galeno</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>11/09/2025</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>179751</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000194", "fecha": "11/09/2025", "cliente": "Sanatorio Galeno", "domicilio": "Av. Belgrano 2970", "localidad": "San Miguel de Tucuman", "cuit": "30-68001836-3", "iva": "Exento", "concepto": "Pago Factura 19423", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 179751.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>0001-00000195</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Farmacia del Jardin</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>12/09/2025</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>207414</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000195", "fecha": "12/09/2025", "cliente": "Farmacia del Jardin", "domicilio": "Av. Siria 1305", "localidad": "San Miguel De Tucuman", "cuit": "20-21328047-4", "iva": "Responsable Inscripto", "concepto": "Pago Factura 19424", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 207414.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>0001-00000196</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Sanatorio Parque S.A.</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>12/09/2025</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>315323.69</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000196", "fecha": "12/09/2025", "cliente": "Sanatorio Parque S.A.", "domicilio": "Santiago y Balcarce", "localidad": "San Miguel De Tucuman", "cuit": "30-61675315-7", "iva": "Responsable Inscripto", "concepto": "Pago Factura 19427", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 315323.69}</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>0001-00000197</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Obra Social de Conductores Camioneros</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>13/09/2025</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>11070</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000197", "fecha": "13/09/2025", "cliente": "Obra Social de Conductores Camioneros", "domicilio": "Catamarca 841", "localidad": "San Miguel de Tucuman", "cuit": "30-66150769-8", "iva": "Exento", "concepto": "Pago Factura 24903", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 11070.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>0001-00000198</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Osperyhra</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>13/09/2025</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>3109840</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000198", "fecha": "13/09/2025", "cliente": "Osperyhra", "domicilio": "Sarmiento 2026", "localidad": "CABA", "cuit": "30-59545956-3", "iva": "Exento", "concepto": "Pago Factura 25076", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 3109840.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>0001-00000199</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Osperyhra</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>13/09/2025</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>690098</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000199", "fecha": "13/09/2025", "cliente": "Osperyhra", "domicilio": "Sarmiento 2026", "localidad": "CABA", "cuit": "30-59545956-3", "iva": "Exento", "concepto": "Pago Factura 25077", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 690098.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>0001-00000200</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Sind. Unico de Trab De Edificios</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>13/09/2025</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>690098</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000200", "fecha": "13/09/2025", "cliente": "Sind. Unico de Trab De Edificios", "domicilio": "Sarmiento 2026", "localidad": "CABA", "cuit": "30-59545956-3", "iva": "Exento", "concepto": "Pago Factura 24242", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 690098.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>0001-00000201</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Sind. Unico de Trab De Edificios</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>13/09/2025</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>690098</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000201", "fecha": "13/09/2025", "cliente": "Sind. Unico de Trab De Edificios", "domicilio": "Salta 450", "localidad": "SMT", "cuit": "30-67535547-5", "iva": "Exento", "concepto": "Pago Factura 24242", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 690098.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>0001-00000202</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Sind. Unico de Trab De Edificios</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>13/09/2025</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>642377.5</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000202", "fecha": "13/09/2025", "cliente": "Sind. Unico de Trab De Edificios", "domicilio": "Salta 450", "localidad": "SMT", "cuit": "30-67535547-5", "iva": "Exento", "concepto": "Pago Factura 24242", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 642377.5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>0001-00000203</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Obra Social Del Personal Prensa</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>15/09/2025</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>264732</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000203", "fecha": "15/09/2025", "cliente": "Obra Social Del Personal Prensa", "domicilio": "Junin 775", "localidad": "San Miguel de Tucuman", "cuit": "30-67540406-9", "iva": "Responsable Inscripto", "concepto": "Pago Factura 24311", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 264732.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>0001-00000204</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Drogueria Suiza</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>15/09/2025</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>1332963.07</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000204", "fecha": "15/09/2025", "cliente": "Drogueria Suiza", "domicilio": "Diagonal Elmina Paz de Gallo 1200", "localidad": "San Miguel de Tucuman", "cuit": "33-54374636-9", "iva": "Responsable Inscripto", "concepto": "Pago Factura 19275 / 19283", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1332963.07}</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>0001-00000206</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Drog. Distribuidora Norte</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>15/09/2025</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>1569498.76</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000206", "fecha": "15/09/2025", "cliente": "Drog. Distribuidora Norte", "domicilio": "Catamarca 24", "localidad": "San Miguel De Tucuman", "cuit": "20-16134777-9", "iva": "Responsable Inscripto", "concepto": "Pago Factura 19239", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1569498.76}</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>0001-00000207</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>O.S.C.T.C.P.</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>15/09/2025</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>63703385.24</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000207", "fecha": "15/09/2025", "cliente": "O.S.C.T.C.P.", "domicilio": "Laprida 366", "localidad": "San Miguel de Tucuman", "cuit": "30-65767771-6", "iva": "Exento", "concepto": "Pago Factura 24386 / 24393 / 24477 / 24478 / 24560 / 24648 / 24651 / 24655 / 24658 / 24659 / 24660 / 24662 /\n24663 / 24690 / 24698 / 24702 / 25356", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 63703385.24}</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>0001-00000208</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>O.S.C.T.C.P.</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>15/09/2025</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>63703385.24</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000208", "fecha": "15/09/2025", "cliente": "O.S.C.T.C.P.", "domicilio": "Laprida 366", "localidad": "San Miguel de Tucuman", "cuit": "30-65767771-6", "iva": "Exento", "concepto": "Pago Factura 24386 / 24393 / 24477 / 24478 / 24560 / 24648 / 24651 / 24655 / 24658 / 24659 / 24660 / 24662 /\n24663 / 24690 / 24698 / 24702 / 25356", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 63703385.24}</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>0001-00000209</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Sanatorio Parque S.A.</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>16/09/2025</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>157125</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000209", "fecha": "16/09/2025", "cliente": "Sanatorio Parque S.A.", "domicilio": "Santiago y Balcarce", "localidad": "San Miguel De Tucuman", "cuit": "30-61675315-7", "iva": "Responsable Inscripto", "concepto": "Pago Factura 19432", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 157125.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>0001-00000210</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>17/09/2025</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>6949190.95</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000210", "fecha": "17/09/2025", "cliente": "Ministerio de Salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago liquidacion 854-2025 / 3459-2024", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 6949190.95}</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>0001-00000211</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>17/09/2025</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>1239007.96</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000211", "fecha": "17/09/2025", "cliente": "Ministerio de Salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago liquidacion 3472-2024", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1239007.96}</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>0001-00000212</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>17/09/2025</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>6324048.18</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000212", "fecha": "17/09/2025", "cliente": "Ministerio de Salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago liquidacion 894-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 6324048.18}</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>0001-00000213</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>17/09/2025</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>24149461.72</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000213", "fecha": "17/09/2025", "cliente": "Ministerio de Salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago liquidacion 915-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 24149461.72}</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>0001-00000214</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>17/09/2025</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>659689.4</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000214", "fecha": "17/09/2025", "cliente": "Ministerio de Salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago liquidacion 3386-2024", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 659689.4}</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>0001-00000215</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Social Med S.R.L.</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>18/09/2025</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>124266.5</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000215", "fecha": "18/09/2025", "cliente": "Social Med S.R.L.", "domicilio": "Salta 78", "localidad": "San Miguel De Tucuman", "cuit": "30-71532612-0", "iva": "Responsable Inscripto", "concepto": "Pago factura 19442", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 124266.5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>0001-00000216</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Hospital Padilla</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>18/09/2025</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>2770415</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000216", "fecha": "18/09/2025", "cliente": "Hospital Padilla", "domicilio": "Alberdi 554", "localidad": "San Miguel de Tucuman", "cuit": "30-69182284-9", "iva": "Exento", "concepto": "Pago factura 23850", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 2770415.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>0001-00000217</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Area Operativa Bella Vista</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>18/09/2025</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>120520</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000217", "fecha": "18/09/2025", "cliente": "Area Operativa Bella Vista", "domicilio": "San Martin 250", "localidad": "Bella Vista", "cuit": "30-69182284-9", "iva": "Exento", "concepto": "Pago factura 24809", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 120520.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>0001-00000218</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Drog. Novamed</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>18/09/2025</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>281000</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000218", "fecha": "18/09/2025", "cliente": "Drog. Novamed", "domicilio": "Batalla de Suipacha 624", "localidad": "San Miguel De Tucuman", "cuit": "20-29507275-0", "iva": "Responsable Inscripto", "concepto": "Pago factura 19425", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 281000.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>0001-00000219</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Dr. Felipe S. Palazzo</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>19/09/2025</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>6220.8</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000219", "fecha": "19/09/2025", "cliente": "Dr. Felipe S. Palazzo", "domicilio": "Sarmiento 157", "localidad": "San Miguel de Tucuman", "cuit": "20-22073820-6", "iva": "Responsable Inscripto", "concepto": "Pago Factura 19443", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 6220.8}</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>0001-00000220</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Aliar S.A.</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>19/09/2025</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>6145213.74</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000220", "fecha": "19/09/2025", "cliente": "Aliar S.A.", "domicilio": "Sarmiento 157", "localidad": "San Miguel de Tucuman", "cuit": "30-70792118-4", "iva": "Responsable Inscripto", "concepto": "Pago Factura 19306 / 19351", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 6145213.74}</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>0001-00000221</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Mutual de la Asoc. Bancaria SMT</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>19/09/2025</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>608740</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000221", "fecha": "19/09/2025", "cliente": "Mutual de la Asoc. Bancaria SMT", "domicilio": "San Martin 469", "localidad": "San Miguel de Tucuman", "cuit": "30-65479852-0", "iva": "Responsable Inscripto", "concepto": "Pago Factura 26026", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 608740.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>0001-00000222</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Ministerio de salud</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>20/09/2025</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>217139.36</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000222", "fecha": "20/09/2025", "cliente": "Ministerio de salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago liquidacion 3488-2024", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 217139.36}</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>0001-00000223</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Ministerio de salud</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>20/09/2025</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>279456</v>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000223", "fecha": "20/09/2025", "cliente": "Ministerio de salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago liquidacion 947-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 279456.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>0001-00000224</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Bramed</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>20/09/2025</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>59243.21</v>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000224", "fecha": "20/09/2025", "cliente": "Bramed", "domicilio": "Monteagudo y Marcos Paz", "localidad": "San Miguel de Tucuman", "cuit": "30-71073853-6", "iva": "Exento", "concepto": "Pago factura 18917", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 59243.21}</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>0001-00000225</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Cofaral</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>20/09/2025</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>822284</v>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000225", "fecha": "20/09/2025", "cliente": "Cofaral", "domicilio": "Catamarca 1053", "localidad": "SMT", "cuit": "30-85896356-9", "iva": "Exento", "concepto": "Pago factura 19392", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 822284.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>0001-00000226</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Cofaral</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>20/09/2025</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>6128355.04</v>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000226", "fecha": "20/09/2025", "cliente": "Cofaral", "domicilio": "Catamarca 1053", "localidad": "SMT", "cuit": "30-85896356-9", "iva": "Exento", "concepto": "Pago factura 19415", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 6128355.04}</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>0001-00000227</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>DR. Felipe S. Palazzo</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>20/09/2025</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>7512.75</v>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000227", "fecha": "20/09/2025", "cliente": "DR. Felipe S. Palazzo", "domicilio": "Catamarca 1053", "localidad": "San Miguel de Tucuman", "cuit": "20-22073820-6", "iva": "Responsable Inscripto", "concepto": "Pago factura 19446", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 7512.75}</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>0001-00000228</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Farmacia Esencial</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>20/09/2025</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>25625</v>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000228", "fecha": "20/09/2025", "cliente": "Farmacia Esencial", "domicilio": "Av. Mate de Luna 4089", "localidad": "San Miguel de Tucuman", "cuit": "30-71571717-0", "iva": "Responsable Inscripto", "concepto": "Pago factura 19448", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 25625.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>0001-00000229</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Farmacia Torres SRL</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>22/09/2025</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>79384.5</v>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000229", "fecha": "22/09/2025", "cliente": "Farmacia Torres SRL", "domicilio": "Uttinger 99", "localidad": "Tafi Viejo", "cuit": "30-71455367-0", "iva": "Responsable Inscripto", "concepto": "Pago factura 19450", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 79384.5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>0001-00000230</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Instituto de Psicopatologia S.R.L.</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>22/09/2025</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>941546.6</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000230", "fecha": "22/09/2025", "cliente": "Instituto de Psicopatologia S.R.L.", "domicilio": "San Martin 141", "localidad": "S.S. de Jujuy", "cuit": "30-61200292-0", "iva": "Exento", "concepto": "Pago factura 25617", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 941546.6}</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>0001-00000231</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Hospital Centro de Salud</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>25/09/2025</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>13503650</v>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000231", "fecha": "25/09/2025", "cliente": "Hospital Centro de Salud", "domicilio": "Av. Avellaneda 750", "localidad": "San Miguel de Tucuman", "cuit": "30691822849", "iva": "Exento", "concepto": "Pago factura 25176", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 13503650.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>0001-00000232</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Farmacia Nueva</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>26/09/2025</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>14113392.08</v>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000232", "fecha": "26/09/2025", "cliente": "Farmacia Nueva", "domicilio": "Lavalle 999", "localidad": "San Miguel De Tucuman", "cuit": "27-29917697-0", "iva": "Responsable Inscripto", "concepto": "Pago Factura 19468", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 14113392.08}</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>0001-00000233</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Farmacia Nueva</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>26/09/2025</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>1521036.73</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000233", "fecha": "26/09/2025", "cliente": "Farmacia Nueva", "domicilio": "Lavalle 999", "localidad": "San Miguel De Tucuman", "cuit": "27-29917697-0", "iva": "Responsable Inscripto", "concepto": "Pago Factura 19467", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1521036.73}</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>0001-00000234</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Farmacia Nueva</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>26/09/2025</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>14113392.08</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000234", "fecha": "26/09/2025", "cliente": "Farmacia Nueva", "domicilio": "Lavalle 999", "localidad": "San Miguel De Tucuman", "cuit": "27-29917697-0", "iva": "Responsable Inscripto", "concepto": "Pago Factura 19468", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 14113392.08}</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>0001-00000235</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Drog. Distribuidora Norte</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>26/09/2025</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>2348836.73</v>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000235", "fecha": "26/09/2025", "cliente": "Drog. Distribuidora Norte", "domicilio": "Catamarca 24", "localidad": "San Miguel De Tucuman", "cuit": "20-16134777-9", "iva": "Responsable Inscripto", "concepto": "Pago Factura 19459", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 2348836.73}</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>0001-00000236</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>26/09/2025</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>37361</v>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000236", "fecha": "26/09/2025", "cliente": "Ministerio de Salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago Liquidacion 3513-2024", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 37361.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>0001-00000237</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>O.S. Del Personal Mosaista</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>4350000</v>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000237", "fecha": "30/09/2025", "cliente": "O.S. Del Personal Mosaista", "domicilio": "Quirno 89", "localidad": "CABA", "cuit": "30-60658818-2", "iva": "Inscripto", "concepto": "Pago facturas 24556 ($1.349.382)/ 24653 ($58.114)/ 24701 ($1.397.096)/ 24767 ($59.567)/ 24782 ($58.114)/\n24792 ($4974)/ 24797 ($118.000)/ 24801 ($5182)/ 24846 ($439.748)/ 24925 ($735.561) / 24961 ($59.567)/\n24962 ($4974) / 24963 ($5182)/ 25041 ($5207)/ 25091 ($5207)/ 25092 ($4.636)/ 25126 ($5182)/ 25127\n($34.307)", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 4350000.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>0001-00000238</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Sanatorio Parque S.A.</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>157125</v>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000238", "fecha": "30/09/2025", "cliente": "Sanatorio Parque S.A.", "domicilio": "Santiago y Balcarce", "localidad": "San Miguel De Tucuman", "cuit": "30-61675315-7", "iva": "Responsable Inscripto", "concepto": "Pago factura 19477", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 157125.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>0001-00000239</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Fcia Universidad</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>26900882.35</v>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000239", "fecha": "30/09/2025", "cliente": "Fcia Universidad", "domicilio": "San Martin 864", "localidad": "San Miguel de Tucuman", "cuit": "30-54667048-8", "iva": "Responsable Inscripto", "concepto": "Pago factura 19307 / 19308 / 19311 / 19312 / 19314 / 19319 / 19320 / 19327 / 19336 / 19337 / 19339 / 19345 /\n19346 / 19348 / 19352 / 19357 / 19358 / 19362 / 19366 / 19367 / 19376 / 19377 / 19382", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 26900882.35}</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>0001-00000240</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>DR. Felipe S. Palazzo</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>127641.83</v>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000240", "fecha": "30/09/2025", "cliente": "DR. Felipe S. Palazzo", "domicilio": "Catamarca 1053", "localidad": "San Miguel de Tucuman", "cuit": "20-22073820-6", "iva": "Responsable Inscripto", "concepto": "Pago factura 19479", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 127641.83}</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>0001-00000241</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Bramed</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>399372.41</v>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000241", "fecha": "01/10/2025", "cliente": "Bramed", "domicilio": "Monteagudo y Marcos Paz", "localidad": "San Miguel de Tucuman", "cuit": "30-71073853-6", "iva": "Responsable Inscripto", "concepto": "Pago Factura 19259 / 19265 / 19267 / 19289", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 399372.41}</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>0001-00000242</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Hospital Padilla</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>903900</v>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000242", "fecha": "01/10/2025", "cliente": "Hospital Padilla", "domicilio": "Alberdi 550", "localidad": "San Miguel de Tucuman", "cuit": "30-69182284-9", "iva": "Exento", "concepto": "Pago Factura 25846", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 903900.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>0001-00000243</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Sanatorio Modelo</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>26187.5</v>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000243", "fecha": "01/10/2025", "cliente": "Sanatorio Modelo", "domicilio": "25 de Mayo 559", "localidad": "San Miguel de Tucuman", "cuit": "30-546000294-9", "iva": "Responsable Inscripto", "concepto": "Pago Factura 19485", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 26187.5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>0001-00000244</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Farmacia El Condor S.C.S.</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>02/10/2025</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>118319.13</v>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000244", "fecha": "02/10/2025", "cliente": "Farmacia El Condor S.C.S.", "domicilio": "Alberdi 489", "localidad": "San Miguel de Tucuman", "cuit": "30-56202047-7", "iva": "Responsable Inscripto", "concepto": "Pago Factura 19486", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 118319.13}</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>0001-00000245</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Area Operativa Bella Vista</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>02/10/2025</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>241040</v>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000245", "fecha": "02/10/2025", "cliente": "Area Operativa Bella Vista", "domicilio": "San Martin 250", "localidad": "Bella Vista", "cuit": "30-69182284-9", "iva": "Exento", "concepto": "Pago Factura 25140", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 241040.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>0001-00000246</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Farmacia Libertad</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>02/10/2025</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000246", "fecha": "02/10/2025", "cliente": "Farmacia Libertad", "domicilio": "San Martin y Marconi", "localidad": "Bella Vista", "cuit": "23-21867677-4", "iva": "Responsable Inscripto", "concepto": "Pago Factura 19484", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1950.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>0001-00000247</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Ricardo C. Mora y CIA SRL</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>02/10/2025</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>1550355.48</v>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000247", "fecha": "02/10/2025", "cliente": "Ricardo C. Mora y CIA SRL", "domicilio": "9 De julio 68", "localidad": "San Miguel de Tucuman", "cuit": "30-71505876-2", "iva": "Responsable Inscripto", "concepto": "Pago Factura 19490", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1550355.48}</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>0001-00000248</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE PROGRAMA INTEGRADO DE SALUD</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>04/10/2025</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>41387041.36</v>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000248", "fecha": "04/10/2025", "cliente": "DIRECCION GENERAL DE PROGRAMA INTEGRADO DE SALUD", "domicilio": "Combate de las Piedras 626", "localidad": "San Miguel de Tucuman", "cuit": "30-69182284-9", "iva": "Exento", "concepto": "Pago Facturas 24917 / 25025 / 25026 / 25172 / 25242 / 25241 / 25239 / 25240 / 25243 / 25296 / 25283 / 25342 /\n25347 / 25348 / 25345 / 25348 / 25345 / 25351 / 25368 / 25365 / 25372 / 25373 / 25367 / 25022 / 25173 / 25113\n/ 25285 / 25284 / 25350 / 25344 / 25493", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 41387041.36}</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>0001-00000249</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE PROGRAMA INTEGRADO DE SALUD</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>04/10/2025</t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>41387041.36</v>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000249", "fecha": "04/10/2025", "cliente": "DIRECCION GENERAL DE PROGRAMA INTEGRADO DE SALUD", "domicilio": "Combate de las Piedras 626", "localidad": "San Miguel de Tucuman", "cuit": "30-69182284-9", "iva": "Exento", "concepto": "Pago Facturas 24917 / 25025 / 25026 / 25172 / 25242 / 25241 / 25239 / 25240 / 25243 / 25296 / 25283 / 25342 /\n25347 / 25348 / 25351 / 25368 / 25365 / 25372 / 25373 / 25367 / 25022 / 25173 / 25113 / 25285 / 25284 / 25350\n/ 25344 / 25493", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 41387041.36}</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>0001-00000250</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>37361</v>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000250", "fecha": "06/10/2025", "cliente": "Ministerio de Salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago liquidacion 3513-2024", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 37361.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>0001-00000251</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>119588</v>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000251", "fecha": "06/10/2025", "cliente": "Ministerio de Salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago liquidacion 3522-2024", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 119588.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>0001-00000252</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>11965327.87</v>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000252", "fecha": "06/10/2025", "cliente": "Ministerio de Salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago liquidacion 996-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 11965327.87}</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>0001-00000253</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>8288237.24</v>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000253", "fecha": "06/10/2025", "cliente": "Ministerio de Salud", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "Exento", "concepto": "Pago liquidacion 1037-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 8288237.24}</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>0001-00000254</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Cofaral</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>21739920</v>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000254", "fecha": "06/10/2025", "cliente": "Cofaral", "domicilio": "Av. Circunvalacion ruta 9 KM 1294", "localidad": "SMT", "cuit": "30-51970271-8", "iva": "Exento", "concepto": "Pago facturas 19431", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 21739920.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>0001-00000255</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Hospital Del Niño</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>2259902</v>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000255", "fecha": "06/10/2025", "cliente": "Hospital Del Niño", "domicilio": "Psj. Hungria 750", "localidad": "SMT", "cuit": "30-69182284-9", "iva": "Exento", "concepto": "Pago facturas 25338 / 25234 / 25174", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 2259902.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>0001-00000256</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Cofaral</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>21739920</v>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000256", "fecha": "06/10/2025", "cliente": "Cofaral", "domicilio": "Av. Circunvalacion ruta 9 KM 1294", "localidad": "SMT", "cuit": "30-51970271-8", "iva": "Exento", "concepto": "Pago facturas 19431", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 21739920.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>0001-00000257</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Bradel Del Pueblo</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>07/10/2025</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>116018.33</v>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000257", "fecha": "07/10/2025", "cliente": "Bradel Del Pueblo", "domicilio": "Av. Alem 199", "localidad": "San Miguel de Tucuman", "cuit": "33-70241330-9", "iva": "Responsable Inscripto", "concepto": "Pago Factura 19400", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 116018.33}</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>0001-00000258</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Farmacia Daruich</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>07/10/2025</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>3087405</v>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000258", "fecha": "07/10/2025", "cliente": "Farmacia Daruich", "domicilio": "Localidad:", "localidad": "CUIT:", "cuit": "", "iva": "Recibimos la suma de pesos:", "concepto": "Pago medicamento eylia", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 3087405.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>0001-00000259</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Obra Social del Personal Prensa</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>08/10/2025</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>1662992</v>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000259", "fecha": "08/10/2025", "cliente": "Obra Social del Personal Prensa", "domicilio": "Junin 775", "localidad": "San Miguel de Tucuman", "cuit": "30-67540406-9", "iva": "Responsable Inscripto", "concepto": "Pago factura 26121", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1662992.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>0001-00000260</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Obra Social del Personal Prensa</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>08/10/2025</t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>1084696</v>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000260", "fecha": "08/10/2025", "cliente": "Obra Social del Personal Prensa", "domicilio": "Junin 775", "localidad": "San Miguel de Tucuman", "cuit": "30-67540406-9", "iva": "Responsable Inscripto", "concepto": "Pago factura 26120", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1084696.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>0001-00000261</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Cofaral</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>21739920</v>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000261", "fecha": "30/09/2025", "cliente": "Cofaral", "domicilio": "Catamarca 1053", "localidad": "San Miguel de Tucuman", "cuit": "30-51970271-8", "iva": "Responsable Inscripto", "concepto": "Pago factura 19431", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 21739920.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>0001-00000262</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>DIR. GRAL. CONTRATACIONES Y ALMACENES</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>07/10/2025</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>2913240</v>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000262", "fecha": "07/10/2025", "cliente": "DIR. GRAL. CONTRATACIONES Y ALMACENES", "domicilio": "LAS PIEDRAS 626", "localidad": "SAN MIGUEL DE TUCUMAN", "cuit": "30-69182284-9", "iva": "Recibimos la suma de pesos:", "concepto": "PAGO FACTURA 24802", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 2913240.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>0001-00000263</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>DIR. GRAL. CONTRATACIONES Y ALMACENES</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>07/10/2025</t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>2482422</v>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000263", "fecha": "07/10/2025", "cliente": "DIR. GRAL. CONTRATACIONES Y ALMACENES", "domicilio": "LAS PIEDRAS 626", "localidad": "SAN MIGUEL DE TUCUMAN", "cuit": "30-69182284-9", "iva": "Recibimos la suma de pesos:", "concepto": "PAGO FACTURA 24799", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 2482422.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>0001-00000264</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>DIR. GRAL. CONTRATACIONES Y ALMACENES</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>07/10/2025</t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>6599004</v>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000264", "fecha": "07/10/2025", "cliente": "DIR. GRAL. CONTRATACIONES Y ALMACENES", "domicilio": "LAS PIEDRAS 626", "localidad": "SAN MIGUEL DE TUCUMAN", "cuit": "30-69182284-9", "iva": "Recibimos la suma de pesos:", "concepto": "PAGO FACTURA 24803", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 6599004.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>0001-00000265</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>DIR. GRAL. CONTRATACIONES Y ALMACENES</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>07/10/2025</t>
+        </is>
+      </c>
+      <c r="E265" t="n">
+        <v>723120</v>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000265", "fecha": "07/10/2025", "cliente": "DIR. GRAL. CONTRATACIONES Y ALMACENES", "domicilio": "LAS PIEDRAS 626", "localidad": "SAN MIGUEL DE TUCUMAN", "cuit": "30-69182284-9", "iva": "Recibimos la suma de pesos:", "concepto": "PAGO FACTURA 24897", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 723120.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>0001-00000266</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>DIR. GRAL. CONTRATACIONES Y ALMACENES</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>07/10/2025</t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>5677835</v>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000266", "fecha": "07/10/2025", "cliente": "DIR. GRAL. CONTRATACIONES Y ALMACENES", "domicilio": "LAS PIEDRAS 626", "localidad": "SAN MIGUEL DE TUCUMAN", "cuit": "30-69182284-9", "iva": "Recibimos la suma de pesos:", "concepto": "PAGO FACTURA 24897", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 5677835.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>0001-00000267</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>DIR. GRAL. CONTRATACIONES Y ALMACENES</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>07/10/2025</t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>5677835</v>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000267", "fecha": "07/10/2025", "cliente": "DIR. GRAL. CONTRATACIONES Y ALMACENES", "domicilio": "LAS PIEDRAS 626", "localidad": "SAN MIGUEL DE TUCUMAN", "cuit": "30-69182284-9", "iva": "Recibimos la suma de pesos:", "concepto": "PAGO FACTURA 24932", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 5677835.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>0001-00000268</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>DIR. GRAL. CONTRATACIONES Y ALMACENES</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>07/10/2025</t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>1478481</v>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000268", "fecha": "07/10/2025", "cliente": "DIR. GRAL. CONTRATACIONES Y ALMACENES", "domicilio": "LAS PIEDRAS 626", "localidad": "SAN MIGUEL DE TUCUMAN", "cuit": "30-69182284-9", "iva": "Recibimos la suma de pesos:", "concepto": "PAGO FACTURA 25037", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1478481.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>0001-00000269</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>DIR. GRAL. CONTRATACIONES Y ALMACENES</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>07/10/2025</t>
+        </is>
+      </c>
+      <c r="E269" t="n">
+        <v>1548096</v>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000269", "fecha": "07/10/2025", "cliente": "DIR. GRAL. CONTRATACIONES Y ALMACENES", "domicilio": "LAS PIEDRAS 626", "localidad": "SAN MIGUEL DE TUCUMAN", "cuit": "30-69182284-9", "iva": "Recibimos la suma de pesos:", "concepto": "PAGO FACTURA 25038", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1548096.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>0001-00000270</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>DIR. GRAL. CONTRATACIONES Y ALMACENES</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>07/10/2025</t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>5439458</v>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000270", "fecha": "07/10/2025", "cliente": "DIR. GRAL. CONTRATACIONES Y ALMACENES", "domicilio": "LAS PIEDRAS 626", "localidad": "SAN MIGUEL DE TUCUMAN", "cuit": "30-69182284-9", "iva": "Recibimos la suma de pesos:", "concepto": "PAGO FACTURA 24811", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 5439458.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>0001-00000271</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>10544</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>07/10/2025</t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>419406.84</v>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000271", "fecha": "07/10/2025", "cliente": "10544", "domicilio": "25 DE MAYO 90 PB", "localidad": "TUCUMAN", "cuit": "30-64542808-1", "iva": "Recibimos la suma de pesos:", "concepto": "PAGO FACTURA 21193/21606/21607/22767/23296", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 419406.84}</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>0001-00000272</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE SALUD</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="E272" t="n">
+        <v>419406.84</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000272", "fecha": "13/10/2025", "cliente": "MINISTERIO DE SALUD", "domicilio": "25 DE MAYO 90 PB", "localidad": "TUCUMAN", "cuit": "30-64542808-1", "iva": "Exento", "concepto": "PAGO LIQ.3556-2024", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 419406.84}</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>0001-00000273</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE SALUD</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>17353094.4</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000273", "fecha": "13/10/2025", "cliente": "MINISTERIO DE SALUD", "domicilio": "25 DE MAYO 90 PB", "localidad": "TUCUMAN", "cuit": "30-64542808-1", "iva": "Exento", "concepto": "PAGO LIQ.1163-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 17353094.4}</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>0001-00000274</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE SALUD</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>1799872</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000274", "fecha": "13/10/2025", "cliente": "MINISTERIO DE SALUD", "domicilio": "25 DE MAYO 90 PB", "localidad": "TUCUMAN", "cuit": "30-64542808-1", "iva": "Exento", "concepto": "PAGO LIQ.1053-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1799872.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>0001-00000275</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE SALUD</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="E275" t="n">
+        <v>7574680.79</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000275", "fecha": "13/10/2025", "cliente": "MINISTERIO DE SALUD", "domicilio": "25 DE MAYO 90 PB", "localidad": "TUCUMAN", "cuit": "30-64542808-1", "iva": "Exento", "concepto": "PAGO LIQ.1077-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 7574680.79}</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>0001-00000276</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>SANATORIO 9 DE JULIO</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>14/10/2025</t>
+        </is>
+      </c>
+      <c r="E276" t="n">
+        <v>6669348.7</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000276", "fecha": "14/10/2025", "cliente": "SANATORIO 9 DE JULIO", "domicilio": "25 MAYO 372", "localidad": "SAN MIGUEL DE TUCUMAN", "cuit": "30-54597921-3", "iva": "RESPONSABLE INSCRIPTO", "concepto": "FAGO FACTURA 19403", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 6669348.7}</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>0001-00000277</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>OBRA SOCIAL DEL PERSONAL PRENSA</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>15/10/2025</t>
+        </is>
+      </c>
+      <c r="E277" t="n">
+        <v>116715</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000277", "fecha": "15/10/2025", "cliente": "OBRA SOCIAL DEL PERSONAL PRENSA", "domicilio": "Junin 775", "localidad": "San Miguel de Tucuman", "cuit": "30-67540406-9", "iva": "Responsable Inscripto", "concepto": "PAGO FACTURA 25872 / 25873", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 116715.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>0001-00000278</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE SALUD</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>15/10/2025</t>
+        </is>
+      </c>
+      <c r="E278" t="n">
+        <v>668373.84</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000278", "fecha": "15/10/2025", "cliente": "MINISTERIO DE SALUD", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67540406-9", "iva": "Responsable Inscripto", "concepto": "PAGO FACTURA 21441/22019/23286/23291/23385", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 668373.84}</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>0001-00000279</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE SALUD</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>15/10/2025</t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>2841000.79</v>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000279", "fecha": "15/10/2025", "cliente": "MINISTERIO DE SALUD", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67540406-9", "iva": "Responsable Inscripto", "concepto": "PAGO FACTURA 22022/22762/22764/23527/23523/23761/23570/23762/24016/24022/24041/24031/24035/24194/24413/24410/24408/24422", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 2841000.79}</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>0001-00000280</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE SALUD</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>15/10/2025</t>
+        </is>
+      </c>
+      <c r="E280" t="n">
+        <v>2841000.79</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000280", "fecha": "15/10/2025", "cliente": "MINISTERIO DE SALUD", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67540406-9", "iva": "Responsable Inscripto", "concepto": "PAGO FACTURA 22022/22762/22764/23527/23523/23761/23570/23762/24016/24022/24041/24031/24035/24194/24413/24410/24408/24422", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 2841000.79}</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>0001-00000281</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE SALUD</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>15/10/2025</t>
+        </is>
+      </c>
+      <c r="E281" t="n">
+        <v>8120710.47</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000281", "fecha": "15/10/2025", "cliente": "MINISTERIO DE SALUD", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67540406-9", "iva": "Responsable Inscripto", "concepto": "PAGO FACTURA 25221/25222/25223/25225/25301/25257/25256/25255/25258/25262/25260/25259/25261/25249/25310/25307/25316/25308/25314/25309/25458/25469/25473/25417/25411/25472/25412/25470/25471/25451/25408/25415/25414/25410/25453/25475/25452/25433", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 8120710.47}</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>0001-00000282</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE SALUD</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>15/10/2025</t>
+        </is>
+      </c>
+      <c r="E282" t="n">
+        <v>6642217.93</v>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000282", "fecha": "15/10/2025", "cliente": "MINISTERIO DE SALUD", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67540406-9", "iva": "Responsable Inscripto", "concepto": "PAGO FACTURA 21092/21551/22294/22954/23114/23101/23097/23190/23507/23459/23504/23472/23462/23428/23449/23512/23595/23787/23794/24058/24493/24462/24616", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 6642217.93}</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>0001-00000283</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>DROG. BELGRANO</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>16/10/2025</t>
+        </is>
+      </c>
+      <c r="E283" t="n">
+        <v>5167538.21</v>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000283", "fecha": "16/10/2025", "cliente": "DROG. BELGRANO", "domicilio": "GUEMES 1040", "localidad": "JUJUY", "cuit": "30-53189257-3", "iva": "RESPONZABLE INSCRIPTO", "concepto": "19184", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 5167538.21}</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>0001-00000284</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>O.S. EMP. DE LA IND. DEL VIDRIO</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>16/10/2025</t>
+        </is>
+      </c>
+      <c r="E284" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000284", "fecha": "16/10/2025", "cliente": "O.S. EMP. DE LA IND. DEL VIDRIO", "domicilio": "AV. CARABOBO 217", "localidad": "CUIT:      30-67896691-2", "cuit": "30-67896691-2", "iva": "RESPONZABLE INSCRIPTO", "concepto": "19182", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1350000.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>0001-00000285</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Hospital Centro De Salud</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="E285" t="n">
+        <v>10134500</v>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000285", "fecha": "17/10/2025", "cliente": "Hospital Centro De Salud", "domicilio": "Av. Avellaneda 750", "localidad": "San Miguel de Tucuman", "cuit": "30691822849", "iva": "Exento", "concepto": "Pago Factura N°25428", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 10134500.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>0001-00000286</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>O.S. EMPLEADOS MARINA MERCANTE</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="E286" t="n">
+        <v>1280270</v>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000286", "fecha": "17/10/2025", "cliente": "O.S. EMPLEADOS MARINA MERCANTE", "domicilio": "BARTOLOME MITRE", "localidad": "CABA", "cuit": "30-59158576-9", "iva": "INSCRIPTO", "concepto": "Pago Factura N°24366 ($ 4947.00)/24378( $276294.00)/24550 ( $ 4974.00 )/24689 ($5638.00)/24704 ($4636.00)/24973 ($66040.00)/25020 ($4623.00)/25189 ($413640.00)/25287 ($4737.00)/25357 ($423932.00)/25726 ($4737.00/25732 ($66072.00)", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1280270.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>0001-00000287</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>O.S. EMP. MARINA MERCANTE</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="E287" t="n">
+        <v>1280270</v>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000287", "fecha": "17/10/2025", "cliente": "O.S. EMP. MARINA MERCANTE", "domicilio": "BARTOLOME MITRE 3776", "localidad": "CABA", "cuit": "30-59158576-9", "iva": "INSCRIPTO", "concepto": "Pago Factura N°24366 ($ 4947.00)/24378( $276294.00)/24550 ( $ 4974.00 )/24689 ($5638.00)/24704 ($4636.00)/24973 ($66040.00)/25020 ($4623.00)/25189 ($413640.00)/25287 ($4737.00)/25357 ($423932.00)/25726 ($4737.00/25732 ($66072.00)", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1280270.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>0001-00000288</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>INSTITUTO DE MATERNIDAD</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="E288" t="n">
+        <v>6146520</v>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000288", "fecha": "17/10/2025", "cliente": "INSTITUTO DE MATERNIDAD", "domicilio": "AV MATE DE LUNA 1551", "localidad": "SAN MIGUEL DE TUCUMAN", "cuit": "30-69182284-9", "iva": "EXENTO", "concepto": "Pago factura N° 25175/25383", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 6146520.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>0001-00000289</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>DROG. NOVAMED DE SANTIADO ROSSI</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="E289" t="n">
+        <v>5019000</v>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000289", "fecha": "17/10/2025", "cliente": "DROG. NOVAMED DE SANTIADO ROSSI", "domicilio": "BATALLA DE SUIPACHA 624", "localidad": "SAN MIGUEL DE TUCUMAN", "cuit": "20-29507275-0", "iva": "RESPONSABLE INSCRIPTO", "concepto": "PAGO FACTURA N° 19529", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 5019000.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>0001-00000291</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>HOSPITAL PABLO SORIA</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="E290" t="n">
+        <v>4031504</v>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000291", "fecha": "17/10/2025", "cliente": "HOSPITAL PABLO SORIA", "domicilio": "SAN SALVADOR DE JUJUY", "localidad": "JUJUY", "cuit": "30-63809244-8", "iva": "RESPONSABLE INSCRIPTO", "concepto": "PAGO FACTURA N° 22205", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 4031504.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>0001-00000292</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>HOSPITAL PABLO SORIA</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="E291" t="n">
+        <v>5674920</v>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000292", "fecha": "17/10/2025", "cliente": "HOSPITAL PABLO SORIA", "domicilio": "SAN SALVADOR DE JUJUY", "localidad": "JUJUY", "cuit": "30-63809244-8", "iva": "RESPONSABLE INSCRIPTO", "concepto": "PAGO FACTURA N° 24224", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 5674920.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>0001-00000293</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>HOSPITAL PABLO SORIA</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="E292" t="n">
+        <v>6468400</v>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000293", "fecha": "17/10/2025", "cliente": "HOSPITAL PABLO SORIA", "domicilio": "SAN SALVADOR DE JUJUY", "localidad": "JUJUY", "cuit": "30-63809244-8", "iva": "RESPONSABLE INSCRIPTO", "concepto": "PAGO FACTURA N° 24922", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 6468400.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>0001-00000294</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Prueba</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>18/10/2025</t>
+        </is>
+      </c>
+      <c r="E293" t="n">
+        <v>0</v>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000294", "fecha": "18/10/2025", "cliente": "Prueba", "domicilio": "Localidad:", "localidad": "CUIT:", "cuit": "", "iva": "Recibimos la suma de pesos:", "concepto": "gggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggggg", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 0.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>0001-00000295</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Prueba</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>18/10/2025</t>
+        </is>
+      </c>
+      <c r="E294" t="n">
+        <v>0</v>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000295", "fecha": "18/10/2025", "cliente": "Prueba", "domicilio": "Localidad:", "localidad": "CUIT:", "cuit": "", "iva": "Recibimos la suma de pesos:", "concepto": "aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 0.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>0001-00000296</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Esto es una prueba</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>18/10/2025</t>
+        </is>
+      </c>
+      <c r="E295" t="n">
+        <v>0</v>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000296", "fecha": "18/10/2025", "cliente": "Esto es una prueba", "domicilio": "Localidad:", "localidad": "CUIT:", "cuit": "", "iva": "Recibimos la suma de pesos:", "concepto": "Pago factura 19307 / 19308 / 19311 / 19312 / 19314 / 19319 / 19320 / 19327 / 19336 / 19337 / 19339 / 19345 /\n19346 / 19348 / 19352 / 19357 / 19358 / 19362 / 19366 / 19367 / 19376 / 19377 / 19382", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 0.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>0001-00000297</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Esto es una prueba</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>18/10/2025</t>
+        </is>
+      </c>
+      <c r="E296" t="n">
+        <v>0</v>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000297", "fecha": "18/10/2025", "cliente": "Esto es una prueba", "domicilio": "Localidad:", "localidad": "CUIT:", "cuit": "", "iva": "Recibimos la suma de pesos:", "concepto": "aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa\naaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa\naaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa\naaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 0.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>0001-00000298</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>FCIA UNIVERSIDAD NAC TUCUMAN</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="E297" t="n">
+        <v>17509510.03</v>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000298", "fecha": "20/10/2025", "cliente": "FCIA UNIVERSIDAD NAC TUCUMAN", "domicilio": "SAN MARTIN 864", "localidad": "SAN MIGUEL DE TUCUMAN", "cuit": "30-54667048-8", "iva": "Recibimos la suma de pesos:", "concepto": "PAGO FACTURA 19383/19391/19411/19428/19455/19385/19395/19412/19439/19460/19389/19398/19418/194\n41/19471/19390/19399/19421/19454/19472", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 17509510.03}</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>0001-00000299</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>AREA OPERATIVA BELLA VISTA</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="E298" t="n">
+        <v>17509510.03</v>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000299", "fecha": "20/10/2025", "cliente": "AREA OPERATIVA BELLA VISTA", "domicilio": "SAN MARTIN N° 250", "localidad": "BELLA VISTA", "cuit": "30-69182284-9", "iva": "EXENTO", "concepto": "PAGO FACTURA 25381", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 17509510.03}</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>0001-00000300</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>HOSPITAL LOMAS DE TAFI</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="E299" t="n">
+        <v>180780</v>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000300", "fecha": "20/10/2025", "cliente": "HOSPITAL LOMAS DE TAFI", "domicilio": "AVDA RAUL ALFONSIN SN ENTRE BATALLA", "localidad": "TAFI VIEJO", "cuit": "30-69182284-9", "iva": "EXENTO", "concepto": "PAGO FACTURA 25029", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 180780.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>0001-00000301</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>HOSPITAL LOMAS DE TAFI</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="E300" t="n">
+        <v>361560</v>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000301", "fecha": "20/10/2025", "cliente": "HOSPITAL LOMAS DE TAFI", "domicilio": "AVDA RAUL ALFONSIN SN ENTRE BATALLA", "localidad": "TAFI VIEJO", "cuit": "30-69182284-9", "iva": "EXENTO", "concepto": "PAGO FACTURA 25192", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 361560.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>0001-00000302</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Bradel Del Pueblo</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="E301" t="n">
+        <v>5434980</v>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000302", "fecha": "20/10/2025", "cliente": "Bradel Del Pueblo", "domicilio": "Av. Alem 199", "localidad": "San Miguel de Tucuman", "cuit": "33-70241330-9", "iva": "Responsable Inscripto", "concepto": "PAGO FACTURA 19444", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 5434980.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>0001-00000303</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>COFARAL TUCUMAN</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>21/10/2025</t>
+        </is>
+      </c>
+      <c r="E302" t="n">
+        <v>15399110</v>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000303", "fecha": "21/10/2025", "cliente": "COFARAL TUCUMAN", "domicilio": "AVDA CIRCUNVALACION RUTA 9 KM 1294", "localidad": "TUCUMAN", "cuit": "30-51970271-8", "iva": "RESPONZABLE INSCRIPTO", "concepto": "PAGO FACTURA 19476", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 15399110.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>0001-00000304</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>HOSPITAL ANGEL C. PADILLA</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>21/10/2025</t>
+        </is>
+      </c>
+      <c r="E303" t="n">
+        <v>2763364.8</v>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000304", "fecha": "21/10/2025", "cliente": "HOSPITAL ANGEL C. PADILLA", "domicilio": "ALBERDI 550", "localidad": "TUCUMAN", "cuit": "30-63809244-8", "iva": "EXENTO", "concepto": "PAGO FACTURA 25512", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 2763364.8}</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>0001-00000305</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>HOSPITAL EVA PERON</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>21/10/2025</t>
+        </is>
+      </c>
+      <c r="E304" t="n">
+        <v>903900</v>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000305", "fecha": "21/10/2025", "cliente": "HOSPITAL EVA PERON", "domicilio": "RUTA 9 Y CALLE EL CARMEN", "localidad": "BANDA DEL RIO SALI-TUCUMAN", "cuit": "30-69182284-9", "iva": "EXENTO", "concepto": "PAGO FACTURA 25429", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 903900.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>0001-00000306</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>O.S. DEL PERSONAL MOSAISTA</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>22/10/2025</t>
+        </is>
+      </c>
+      <c r="E305" t="n">
+        <v>2618000</v>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000306", "fecha": "22/10/2025", "cliente": "O.S. DEL PERSONAL MOSAISTA", "domicilio": "Quirno 89", "localidad": "CABA", "cuit": "30-60658818-2", "iva": "Inscripto", "concepto": "PAGO FACTURA N° 25127 ($41,893.00)/25132 ($109,935.00)/25139 ( $28,004.00)/25179 ( $4,737.00)/25186 (\n$144,013.00)/25214 ( $4,737.00)/25268 ($117,889.00)/25275 ($102,112.00)/25280 ($100,938.00)/25292\n($59,032.00)/25302 ($5,369.00)25305 ($10,168.00)/25326 ($114,242.00)/25360 ($128,606.00)/25369\n($60,094.00)/25369 ($60,094.00)/25499 ($47,737.00)/25516 ($128,606.00)/25561 ($111,600.00)/25654\n($60,095.00)/25656 ($60,095.00)/25664 ($4,526.00)/25723 ($60,095.00)/25727 ($53,554.00)/25781 ($78,822.00)/25800\n($115,583.00)/25816 ($454,658.00)/25836 ($70,800.00)/25841 ($5,084.00)/25848 ($81,102.00)/25865\n($126,936.00)/25887 ($46,698.00)/25888 ($4,380.00/25950 ($118,860.00).", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 2618000.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>0001-00000307</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE SALUD</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>22/10/2025</t>
+        </is>
+      </c>
+      <c r="E306" t="n">
+        <v>6264542.78</v>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000307", "fecha": "22/10/2025", "cliente": "MINISTERIO DE SALUD", "domicilio": "25 De Mayo 90", "localidad": "SAN MIGUEL DE TUCUMAN", "cuit": "30-67540406-9", "iva": "RESPONSABLE INSCRIPTO", "concepto": "PAGO LIQ. 3605-2024/LIQ. 1302-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 6264542.78}</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>0001-00000308</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE SALUD</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>22/10/2025</t>
+        </is>
+      </c>
+      <c r="E307" t="n">
+        <v>14056994.65</v>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000308", "fecha": "22/10/2025", "cliente": "MINISTERIO DE SALUD", "domicilio": "25 De Mayo 90", "localidad": "SAN MIGUEL DE TUCUMAN", "cuit": "30-67540406-9", "iva": "RESPONSABLE INSCRIPTO", "concepto": "PAGO LIQ. 1293-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 14056994.65}</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>0001-00000309</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE SALUD</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>22/10/2025</t>
+        </is>
+      </c>
+      <c r="E308" t="n">
+        <v>2488868.4</v>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000309", "fecha": "22/10/2025", "cliente": "MINISTERIO DE SALUD", "domicilio": "25 De Mayo 90", "localidad": "SAN MIGUEL DE TUCUMAN", "cuit": "30-67540406-9", "iva": "RESPONSABLE INSCRIPTO", "concepto": "PAGO LIQ. 1263-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 2488868.4}</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>0001-00000310</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE SALUD</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>22/10/2025</t>
+        </is>
+      </c>
+      <c r="E309" t="n">
+        <v>8715147.960000001</v>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000310", "fecha": "22/10/2025", "cliente": "MINISTERIO DE SALUD", "domicilio": "25 De Mayo 90", "localidad": "SAN MIGUEL DE TUCUMAN", "cuit": "30-67540406-9", "iva": "RESPONSABLE INSCRIPTO", "concepto": "PAGO LIQ. 1264-2025", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 8715147.96}</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>0001-00000311</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>HOSPITAL REGIONAL DE CONCEPCION</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>22/10/2025</t>
+        </is>
+      </c>
+      <c r="E310" t="n">
+        <v>1807800</v>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000311", "fecha": "22/10/2025", "cliente": "HOSPITAL REGIONAL DE CONCEPCION", "domicilio": "SAN LUIS 150", "localidad": "CONCEPCION", "cuit": "30-69182284-9", "iva": "RESPONSABLE INSCRIPTO", "concepto": "PAGO FACTURA N° 25380", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1807800.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>0001-00000312</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE PROGRAMA INTEGRADO DE SALUD</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>22/10/2025</t>
+        </is>
+      </c>
+      <c r="E311" t="n">
+        <v>240060</v>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000312", "fecha": "22/10/2025", "cliente": "DIRECCION GENERAL DE PROGRAMA INTEGRADO DE SALUD", "domicilio": "COMBATE DE LAS PIEDRAS 626", "localidad": "SAN MIGUEL DE TUCUMAN", "cuit": "30-69182284-9", "iva": "EXENTO", "concepto": "PAGO FACTURA N° 23204", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 240060.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>0001-00000313</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>HOSPITAL AVELLANEDA</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>23/10/2025</t>
+        </is>
+      </c>
+      <c r="E312" t="n">
+        <v>8731307</v>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000313", "fecha": "23/10/2025", "cliente": "HOSPITAL AVELLANEDA", "domicilio": "CATAMARCA 2000", "localidad": "San Miguel de Tucuman", "cuit": "30-69182284-9", "iva": "Exento", "concepto": "PAGO FACTURA N°25035/25232/25506/25612", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 8731307.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>0001-00000314</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE SALUD</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>23/10/2025</t>
+        </is>
+      </c>
+      <c r="E313" t="n">
+        <v>1594632.38</v>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000314", "fecha": "23/10/2025", "cliente": "MINISTERIO DE SALUD", "domicilio": "25 De Mayo 90", "localidad": "San Miguel de Tucuman", "cuit": "30-67542808-1", "iva": "EXENTO", "concepto": "PAGO LIQ. N° 3583-2024/1072-2025.", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1594632.38}</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>0001-00000315</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE PROGRAMA INTEGRADO DE SALUD</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>23/10/2025</t>
+        </is>
+      </c>
+      <c r="E314" t="n">
+        <v>148955110</v>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000315", "fecha": "23/10/2025", "cliente": "DIRECCION GENERAL DE PROGRAMA INTEGRADO DE SALUD", "domicilio": "COMBATE DE LAS PIEDRAS 626", "localidad": "SAN MIGUEL DE TUCUMAN", "cuit": "30-69182284-9", "iva": "EXENTO", "concepto": "PAGO FACTURA N°24919", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 148955110.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>0001-00000316</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>FARMACIA ESENCIAL</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>23/10/2025</t>
+        </is>
+      </c>
+      <c r="E315" t="n">
+        <v>63402.66</v>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000316", "fecha": "23/10/2025", "cliente": "FARMACIA ESENCIAL", "domicilio": "Av. Mate de Luna 4089", "localidad": "San Miguel de Tucuman", "cuit": "30-71571717-0", "iva": "RESPONSABLE INSCRIPTO", "concepto": "PAGO FACTURA N°19223", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 63402.66}</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>0001-00000317</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>FARMACIA SILOE</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>23/10/2025</t>
+        </is>
+      </c>
+      <c r="E316" t="n">
+        <v>37605.82</v>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000317", "fecha": "23/10/2025", "cliente": "FARMACIA SILOE", "domicilio": "CRISOSTOMO ALVAREZ 960", "localidad": "TUCUMAN", "cuit": "27-11708171-6", "iva": "RESPONSABLE INSCRIPTO", "concepto": "PAGO FACTURA N°19224", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 37605.82}</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>0001-00000318</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>ALIAR S.A.</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>23/10/2025</t>
+        </is>
+      </c>
+      <c r="E317" t="n">
+        <v>8856129.939999999</v>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000318", "fecha": "23/10/2025", "cliente": "ALIAR S.A.", "domicilio": "Sarmiento 157", "localidad": "San Miguel de Tucuman", "cuit": "30-70792118-4", "iva": "Responsable Inscripto", "concepto": "PAGO FACTURAS N° 19407/19437/19436/19478.", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 8856129.94}</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>0001-00000319</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>AREA OPERATIVA AGUILARES</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="E318" t="n">
+        <v>120520</v>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000319", "fecha": "24/10/2025", "cliente": "AREA OPERATIVA AGUILARES", "domicilio": "AVELLANEDA Y J.B. ALBERDI", "localidad": "TUCUMAN", "cuit": "30-69182284-9", "iva": "EXENTO", "concepto": "PAGO FACTURA N°25484", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 120520.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>0001-00000320</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>INSTITUTO DE MATERNIDAD</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="E319" t="n">
+        <v>2711700</v>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000320", "fecha": "24/10/2025", "cliente": "INSTITUTO DE MATERNIDAD", "domicilio": "AV MATE DE LUNA 1551", "localidad": "SAN MIGUEL DE TUCUMAN", "cuit": "30-69182284-9", "iva": "EXENTRO", "concepto": "PAGO FACTURA N°24899", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 2711700.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>0001-00000321</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>DROG. NOVAMED DE SANTIAGO ROSSI</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="E320" t="n">
+        <v>312798</v>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000321", "fecha": "24/10/2025", "cliente": "DROG. NOVAMED DE SANTIAGO ROSSI", "domicilio": "BATALLA DE SUIPACHA 624", "localidad": "SAN MIGUEL DE TUCUMAN", "cuit": "20-29507275-0", "iva": "RESPONSABLE INSCRIPTO", "concepto": "PAGO FACTURA N°19230/19231", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 312798.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>0001-00000322</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>MACROFARMA S.A.</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>25/10/2025</t>
+        </is>
+      </c>
+      <c r="E321" t="n">
+        <v>3468000</v>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000322", "fecha": "25/10/2025", "cliente": "MACROFARMA S.A.", "domicilio": "AVENIDA DE CIRCUNVALACION 1294", "localidad": "SAN MIGUEL DE TUCUMAN", "cuit": "30-70865088-5", "iva": "30-70865088-5", "concepto": "PAGO FACTURA N°19445", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 3468000.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>0001-00000323</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>DIR. GRAL. CONTRATACIONES Y ALMACENES</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="E322" t="n">
+        <v>306591750</v>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000323", "fecha": "27/10/2025", "cliente": "DIR. GRAL. CONTRATACIONES Y ALMACENES", "domicilio": "LAS PIEDRAS 626", "localidad": "SAN MIGUEL DE TUCUMAN", "cuit": "30-69182284-9", "iva": "Recibimos la suma de pesos:", "concepto": "PAGO FACTURA N° 25295", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 306591750.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>0001-00000324</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Obra Social de Personal Prensa</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="E323" t="n">
+        <v>214479</v>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000324", "fecha": "27/10/2025", "cliente": "Obra Social de Personal Prensa", "domicilio": "Junin 775", "localidad": "SAN MIGUEL DE TUCUMAN", "cuit": "30-67540406-9", "iva": "Responsable Inscripto", "concepto": "PAGO FACTURA N°25706", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 214479.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>0001-00000325</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Obra Social de Personal Prensa</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="E324" t="n">
+        <v>40950</v>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000325", "fecha": "27/10/2025", "cliente": "Obra Social de Personal Prensa", "domicilio": "Junin 775", "localidad": "SAN MIGUEL DE TUCUMAN", "cuit": "30-67540406-9", "iva": "Responsable Inscripto", "concepto": "PAGO FACTURA N°26021", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 40950.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>0001-00000326</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>HOSPITAL DEL NIÑO JESUS</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="E325" t="n">
+        <v>309765.44</v>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000326", "fecha": "27/10/2025", "cliente": "HOSPITAL DEL NIÑO JESUS", "domicilio": "PASAJE HUNGRIA 750", "localidad": "SAN MIGUEL DE TUCUMAN", "cuit": "30-69182284-9", "iva": "EXENTO", "concepto": "PAGO FACTURA N°24584", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 309765.44}</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>0001-00000327</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Inst. De Prev. Y Seg. Social De La Prov</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="E326" t="n">
+        <v>399675104.17</v>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000327", "fecha": "27/10/2025", "cliente": "Inst. De Prev. Y Seg. Social De La Prov", "domicilio": "Las Piedras 530", "localidad": "San Miguel de Tucuman", "cuit": "30-63394922-7", "iva": "Exento", "concepto": "PAGO FACTURA N° 24219 / 24221/ 24222 /24223 / 24225.", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 399675104.17}</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>0001-00000328</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Inst. De Prev. Y Seg. Social De La Prov</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="E327" t="n">
+        <v>398804734.92</v>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000328", "fecha": "27/10/2025", "cliente": "Inst. De Prev. Y Seg. Social De La Prov", "domicilio": "Las Piedras 530", "localidad": "San Miguel de Tucuman", "cuit": "30-63394922-7", "iva": "Exento", "concepto": "PAGO FACTURA N° 24388 / 24389 / 24390 / 24391 / 24392 / NCR X DESC. NOVO(-$9153273.13 / NCR\nPRONTO PAGO (-$29599084.61) / NCR X FREESTYLE (-9526215.07) .", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 398804734.92}</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>0001-00000329</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Inst. De Prev y Seg. Social De La Prov</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="E328" t="n">
+        <v>399675104.17</v>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000329", "fecha": "27/10/2025", "cliente": "Inst. De Prev y Seg. Social De La Prov", "domicilio": "Las Piedras 530", "localidad": "San Miguel De Tucuman", "cuit": "30-63394922-7", "iva": "Exento", "concepto": "Pago FACTURA N° 24219 / 24221 / 24222 / 24223 / 24225 / NCR X DIF. PRECIO (-11540301.05) / NCR X\nPRONTO PAGO (-35251257.36) .", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 399675104.17}</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>0001-00000330</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Inst. De Prev y Seg. Social De La Prov</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="E329" t="n">
+        <v>443622590.24</v>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000330", "fecha": "27/10/2025", "cliente": "Inst. De Prev y Seg. Social De La Prov", "domicilio": "Las Piedras 530", "localidad": "San Miguel De Tucuman", "cuit": "30-63394922-7", "iva": "Exento", "concepto": "Pago FACTURA N° 24813 / 24820 / 24822 / 24823 / 24847 / NCR X DESC. NOVO (-$10854576.30) / NCR X\nPRONTO PAGO (-34807798.60) / NCR X FREESTYLE ( - 2452368.00) / NCR DEV ABBOTT (- 10790596.90).", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 443622590.24}</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>0001-00000331</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Inst. De Prev y Seg. Social De La Prov</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="E330" t="n">
+        <v>405750272.65</v>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000331", "fecha": "27/10/2025", "cliente": "Inst. De Prev y Seg. Social De La Prov", "domicilio": "Las Piedras 530", "localidad": "San Miguel De Tucuman", "cuit": "30-63394922-7", "iva": "Exento", "concepto": "Pago FACTURA N° 25121 / 25122 / 25123 / 25124 / 25125 / NCR X DESC NOVO (-10812464.86) / NCR X\nPRONTO PAGO (-34953781.42) / NCR X DEXCOM (-1029775.26).", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 405750272.65}</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>0001-00000332</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>O.S.C.T.C.P. (EX UTA OBRA SOCIAL)</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>28/10/2025</t>
+        </is>
+      </c>
+      <c r="E331" t="n">
+        <v>32834718</v>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>Anulado</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000332", "fecha": "28/10/2025", "cliente": "O.S.C.T.C.P. (EX UTA OBRA SOCIAL)", "domicilio": "LAPRIDA 366", "localidad": "TUCUMAN", "cuit": "30-65767771-6", "iva": "EXENTO", "concepto": "PAGO FACTURA 24768 / 24786 / 24793 /24815/ 27857 /24908/ 24908 /24964 / 24965 / 24966 / 24967 / 24970/\n24975 / 25011 / 25096.", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 32834718.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>0001-00000333</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>OSPERYHNA</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>28/10/2025</t>
+        </is>
+      </c>
+      <c r="E332" t="n">
+        <v>12410546</v>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000333", "fecha": "28/10/2025", "cliente": "OSPERYHNA", "domicilio": "SARMIENTO 2026", "localidad": "CABA", "cuit": "30-59545956-3", "iva": "EXENTO", "concepto": "PAGO FACTURA 25084 / 25117 / 25353 / 25354 / 25359 / 25390 / 25392 / 25393 / 25513 / 25557 / 25750 /\n25818 / 25840 / 25946 / 25951 /26000.", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 12410546.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>0001-00000334</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>O.S.C.T.C.P UTA - SECC. CHACO</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>29/10/2025</t>
+        </is>
+      </c>
+      <c r="E333" t="n">
+        <v>769270</v>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000334", "fecha": "29/10/2025", "cliente": "O.S.C.T.C.P UTA - SECC. CHACO", "domicilio": "ROBERTO MORA 150", "localidad": "RESISTENCIA- CHACO", "cuit": "30-65767771-6", "iva": "EXENTO", "concepto": "PAGO FACTURA N°26373", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 769270.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>0001-00000335</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>O.S. EMPLEADOS DE LA IND. DEL VIDRIO</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>29/10/2025</t>
+        </is>
+      </c>
+      <c r="E334" t="n">
+        <v>865180.02</v>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000335", "fecha": "29/10/2025", "cliente": "O.S. EMPLEADOS DE LA IND. DEL VIDRIO", "domicilio": "AV. CARABOBO N° 217", "localidad": "CABA", "cuit": "30-67896691-2", "iva": "RESPONSABLE INSRIPTO", "concepto": "PAGO FACTURA N° 19182 ($ 787020.00) / 19206 ($59567.00) / 19333 ($18593.02).", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 865180.02}</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>0001-00000336</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>DIR. GRAL. CONTRATACIONES Y ALMACENES</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>29/10/2025</t>
+        </is>
+      </c>
+      <c r="E335" t="n">
+        <v>7575159</v>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000336", "fecha": "29/10/2025", "cliente": "DIR. GRAL. CONTRATACIONES Y ALMACENES", "domicilio": "LAS PIEDRAS 626", "localidad": "SAN MIGUEL DE TUCUMAN", "cuit": "30-69182284-9", "iva": "EXENTO", "concepto": "PAGO FACTURA N° 25352", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 7575159.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>0001-00000337</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE SALUD</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>29/10/2025</t>
+        </is>
+      </c>
+      <c r="E336" t="n">
+        <v>322230.06</v>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000337", "fecha": "29/10/2025", "cliente": "MINISTERIO DE SALUD", "domicilio": "25 DE MAYO 90", "localidad": "SAN MIGUEL DE TUCUMAN", "cuit": "30-67542808-1", "iva": "EXENTO", "concepto": "PAGO FACTURA N° 24414 / 21853 / 21861 / 22360.", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 322230.06}</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>0001-00000338</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE SALUD</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>29/10/2025</t>
+        </is>
+      </c>
+      <c r="E337" t="n">
+        <v>1095642.53</v>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000338", "fecha": "29/10/2025", "cliente": "MINISTERIO DE SALUD", "domicilio": "25 DE MAYO 90", "localidad": "SAN MIGUEL DE TUCUMAN", "cuit": "30-67542808-1", "iva": "EXENTO", "concepto": "PAGO FACTURA N° 23830 / 24426 / 24430 / 24683 / 24569 / 24575 / 25016 / 25013.", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1095642.53}</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>0001-00000339</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE SALUD</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>29/10/2025</t>
+        </is>
+      </c>
+      <c r="E338" t="n">
+        <v>1319749.24</v>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000339", "fecha": "29/10/2025", "cliente": "MINISTERIO DE SALUD", "domicilio": "25 DE MAYO 90", "localidad": "SAN MIGUEL DE TUCUMAN", "cuit": "30-67542808-1", "iva": "EXENTO", "concepto": "PAGO FACTURA N° 24014 / 24018 / 24415 / 24419 / 24409 / 24407 / 24453 / 24435 .", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1319749.24}</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>0001-00000340</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE SALUD</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>29/10/2025</t>
+        </is>
+      </c>
+      <c r="E339" t="n">
+        <v>6674417.1</v>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000340", "fecha": "29/10/2025", "cliente": "MINISTERIO DE SALUD", "domicilio": "25 DE MAYO 90", "localidad": "SAN MIGUEL DE TUCUMAN", "cuit": "30-67542808-1", "iva": "EXENTO", "concepto": "PAGO FACTURA N° 25647 / 25645 / 25622 / 25648 / 25681 / 25690 / 25689 / 25692 / 25691 / 25694 / 25683 /\n25677 / 25678 / 25682 / 25693 / 25684 / 25685 / 25680 / 25695 / 25696 / 25686 / 25697 / 25704 /", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 6674417.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>0001-00000341</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>O.S.C.T.C.P. ( EX  UTA OBRA SOCIAL )</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>29/10/2022</t>
+        </is>
+      </c>
+      <c r="E340" t="n">
+        <v>32834718</v>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000341", "fecha": "29/10/2022", "cliente": "O.S.C.T.C.P. ( EX  UTA OBRA SOCIAL )", "domicilio": "LAPRIDA 366", "localidad": "TUCUMAN", "cuit": "30-65767771-6", "iva": "EXENTO", "concepto": "PAGO FACTURA N° 24768 / 24786 / 24793 / 24815 / 24857 / 24908 / 24964 / 24966 / 24967 / 24970 / 24975 /\n25011 / 24965 / 25096.", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 32834718.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>0001-00000342</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>DROG. TUCUMAN MARTINEZ DULOC ANDREA KARIN</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>30/10/2025</t>
+        </is>
+      </c>
+      <c r="E341" t="n">
+        <v>508762.8</v>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000342", "fecha": "30/10/2025", "cliente": "DROG. TUCUMAN MARTINEZ DULOC ANDREA KARIN", "domicilio": "CORONEL ZELAYA 256", "localidad": "SAN MIGUEL DE TUCUMAN", "cuit": "30-63809244-8", "iva": "RESPONSABLE INSCRIPTO", "concepto": "PAGO FACTURA N° 19519 .", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 508762.8}</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>0001-00000343</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>HOSPITAL ANGEL C. PADILLA</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>30/10/2025</t>
+        </is>
+      </c>
+      <c r="E342" t="n">
+        <v>602600</v>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000343", "fecha": "30/10/2025", "cliente": "HOSPITAL ANGEL C. PADILLA", "domicilio": "ALBERDI 550", "localidad": "TUCUMAN", "cuit": "30-63809244-8", "iva": "EXENTO", "concepto": "PAGO FACTURA N° 25597", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 602600.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>0001-00000344</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>BRAMED RECIBO DE PRUEBA 2</t>
+        </is>
+      </c>
+      <c r="E343" t="n">
+        <v>5555556</v>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000344", "fecha": "", "cliente": "BRAMED RECIBO DE PRUEBA 2", "domicilio": "Monteagudo y Marcos Paz", "localidad": "San Miguel de Tucuman", "cuit": "30-71073853-6", "iva": "Responsable Inscripto", "concepto": "", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 5555556.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>0001-00000345</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>FARMACIA PARIS S.F.T.</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="E344" t="n">
+        <v>3774755.53</v>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000345", "fecha": "31/10/2025", "cliente": "FARMACIA PARIS S.F.T.", "domicilio": "BALCARCE 473", "localidad": "TUCUMAN", "cuit": "30-70809177-0", "iva": "RESPONSABLE INSCRIPTO", "concepto": "PAGO FACTURAS N° 19108 / 19138 / 19147 / 19191 / 19202 / 19204 / 19213 / 19221 / 19257 / 19288 / 19294 /\n19298 / 19302 / 19426 / 19559 .", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 3774755.53}</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>0001-00000346</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>FARMACIA FLEMING</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="E345" t="n">
+        <v>878702.2</v>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000346", "fecha": "31/10/2025", "cliente": "FARMACIA FLEMING", "domicilio": "BELGRANO 674", "localidad": "SALTA", "cuit": "27-20503988-6", "iva": "RESPONSABLE INSCRIPTO", "concepto": "PAGO FACTURA N° 18889 / 18948 / 19031 / 19111 / 19112 .", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 878702.2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>0001-00000347</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Este es un recibo de prueba y vuelvo a probar</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>01/11/2025</t>
+        </is>
+      </c>
+      <c r="E346" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000347", "fecha": "01/11/2025", "cliente": "Este es un recibo de prueba y vuelvo a probar", "domicilio": "Hola", "localidad": "ds", "cuit": "", "iva": "ef", "concepto": "Pago facdawdsa", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 5000.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>0001-00000348</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Soremer</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="E347" t="n">
+        <v>1425777.39</v>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000348", "fecha": "03/11/2025", "cliente": "Soremer", "domicilio": "Monteagudo 815", "localidad": "San Miguel De Tucuman", "cuit": "30-64058584-2", "iva": "Responsable Inscripto", "concepto": "Pago Factura 19583", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1425777.39}</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>0001-00000349</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>O. SOCIAL DE LA UNSA</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="E348" t="n">
+        <v>107940</v>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000349", "fecha": "03/11/2025", "cliente": "O. SOCIAL DE LA UNSA", "domicilio": "BUENOS AIRES 367", "localidad": "SALTA", "cuit": "30-56359651-8", "iva": "RESPONSABLE INSCRIPTO", "concepto": "Pago Factura 19583", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 107940.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>0001-00000350</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>DROG. Y FCIA. SUD AMERICANA S.R.L.</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="E349" t="n">
+        <v>1453033</v>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>{"numero_recibo": "0001-00000350", "fecha": "03/11/2025", "cliente": "DROG. Y FCIA. SUD AMERICANA S.R.L.", "domicilio": "ALBERDI N° 102", "localidad": "SALTA", "cuit": "30-56173408-5", "iva": "RESPONSABLE INSCRIPTO", "concepto": "Pago FaCTURAS N° 19161 / 19180 / 19194 / 19263 / 19271 / 19433 / 19447.", "retenciones": {"Ganancias": 0.0, "SUSS": 0.0, "TEM": 0.0, "IIBB": 0.0}, "forma_pago": [], "total": 1453033.0}</t>
         </is>
       </c>
     </row>
